--- a/data/mpg/mpg_round3_top5_bets.xlsx
+++ b/data/mpg/mpg_round3_top5_bets.xlsx
@@ -106,22 +106,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E2">
@@ -129,66 +129,66 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="H2">
-        <v>0.5469750581767149</v>
+        <v>0.4033014374680687</v>
       </c>
       <c r="I2">
-        <v>91.0</v>
+        <v>108.0</v>
       </c>
       <c r="J2">
-        <v>49.77473029408105</v>
+        <v>43.55655524655142</v>
       </c>
       <c r="K2">
-        <v>0.09982801209349226</v>
+        <v>0.3034148547376874</v>
       </c>
       <c r="L2">
-        <v>0.1752439085943989</v>
+        <v>0.7508755811175876</v>
       </c>
       <c r="M2">
-        <v>0.13979061144940538</v>
+        <v>0.8282858904878876</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="O2">
-        <v>50.0</v>
+        <v>20.0</v>
       </c>
       <c r="P2">
-        <v>4.991400604674613</v>
+        <v>6.068297094753748</v>
       </c>
       <c r="Q2">
-        <v>54.76613089875566</v>
+        <v>49.624852341305164</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E3">
@@ -196,66 +196,66 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="H3">
-        <v>0.5469750581767149</v>
+        <v>0.4033014374680687</v>
       </c>
       <c r="I3">
-        <v>91.0</v>
+        <v>108.0</v>
       </c>
       <c r="J3">
-        <v>49.77473029408105</v>
+        <v>43.55655524655142</v>
       </c>
       <c r="K3">
-        <v>0.13058755997533886</v>
+        <v>0.09260282764414957</v>
       </c>
       <c r="L3">
-        <v>0.22924101105460865</v>
+        <v>0.2291687467989873</v>
       </c>
       <c r="M3">
-        <v>0.20572160842474707</v>
+        <v>0.15556586453121213</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="O3">
-        <v>30.0</v>
+        <v>50.0</v>
       </c>
       <c r="P3">
-        <v>3.917626799260166</v>
+        <v>4.630141382207478</v>
       </c>
       <c r="Q3">
-        <v>53.692357093341215</v>
+        <v>48.186696628758895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E4">
@@ -263,66 +263,66 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="H4">
-        <v>0.5469750581767149</v>
+        <v>0.4033014374680687</v>
       </c>
       <c r="I4">
-        <v>91.0</v>
+        <v>108.0</v>
       </c>
       <c r="J4">
-        <v>49.77473029408105</v>
+        <v>43.55655524655142</v>
       </c>
       <c r="K4">
-        <v>0.05118730378605263</v>
+        <v>0.007432744453083944</v>
       </c>
       <c r="L4">
-        <v>0.08985717533347037</v>
+        <v>0.01839417623548114</v>
       </c>
       <c r="M4">
-        <v>0.09407779892978912</v>
+        <v>0.0156080724814215</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Mega rare</t>
         </is>
       </c>
       <c r="O4">
-        <v>50.0</v>
+        <v>70.0</v>
       </c>
       <c r="P4">
-        <v>2.5593651893026315</v>
+        <v>0.5202921117158761</v>
       </c>
       <c r="Q4">
-        <v>52.334095483383685</v>
+        <v>44.076847358267294</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E5">
@@ -330,66 +330,66 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>3-3</t>
         </is>
       </c>
       <c r="H5">
-        <v>0.5469750581767149</v>
+        <v>0.4033014374680687</v>
       </c>
       <c r="I5">
-        <v>91.0</v>
+        <v>108.0</v>
       </c>
       <c r="J5">
-        <v>49.77473029408105</v>
+        <v>43.55655524655142</v>
       </c>
       <c r="K5">
-        <v>0.035973731579912606</v>
+        <v>0.0006228917335824087</v>
       </c>
       <c r="L5">
-        <v>0.06315038431182596</v>
+        <v>0.0015415006388905632</v>
       </c>
       <c r="M5">
-        <v>0.03148408590568708</v>
+        <v>0.0005232058972133063</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Mega rare</t>
+          <t>Ultra rare</t>
         </is>
       </c>
       <c r="O5">
-        <v>70.0</v>
+        <v>100.0</v>
       </c>
       <c r="P5">
-        <v>2.5181612105938824</v>
+        <v>0.062289173358240864</v>
       </c>
       <c r="Q5">
-        <v>52.292891504674934</v>
+        <v>43.61884441990966</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E6">
@@ -397,66 +397,66 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>4-4</t>
         </is>
       </c>
       <c r="H6">
-        <v>0.5469750581767149</v>
+        <v>0.4033014374680687</v>
       </c>
       <c r="I6">
-        <v>91.0</v>
+        <v>108.0</v>
       </c>
       <c r="J6">
-        <v>49.77473029408105</v>
+        <v>43.55655524655142</v>
       </c>
       <c r="K6">
-        <v>0.12310556433733542</v>
+        <v>7.894543154473964e-06</v>
       </c>
       <c r="L6">
-        <v>0.2161066799966887</v>
+        <v>1.9537012068503745e-05</v>
       </c>
       <c r="M6">
-        <v>0.32322469698103296</v>
+        <v>1.6577806830371323e-05</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Exact</t>
+          <t>Ultra rare</t>
         </is>
       </c>
       <c r="O6">
-        <v>20.0</v>
+        <v>100.0</v>
       </c>
       <c r="P6">
-        <v>2.4621112867467083</v>
+        <v>0.0007894543154473964</v>
       </c>
       <c r="Q6">
-        <v>52.23684158082776</v>
+        <v>43.557344700866864</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E7">
@@ -464,31 +464,31 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="H7">
-        <v>0.5787301755127098</v>
+        <v>0.967577190262213</v>
       </c>
       <c r="I7">
-        <v>87.0</v>
+        <v>56.0</v>
       </c>
       <c r="J7">
-        <v>50.34952526960575</v>
+        <v>54.184322654683925</v>
       </c>
       <c r="K7">
-        <v>0.12246425210248912</v>
+        <v>0.16682026612393575</v>
       </c>
       <c r="L7">
-        <v>0.20330135753186984</v>
+        <v>0.18016441107145345</v>
       </c>
       <c r="M7">
-        <v>0.16216872709277985</v>
+        <v>0.1619452409691271</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -499,31 +499,31 @@
         <v>50.0</v>
       </c>
       <c r="P7">
-        <v>6.123212605124456</v>
+        <v>8.341013306196787</v>
       </c>
       <c r="Q7">
-        <v>56.47273787473021</v>
+        <v>62.52533596088071</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E8">
@@ -531,66 +531,66 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="H8">
-        <v>0.5787301755127098</v>
+        <v>0.967577190262213</v>
       </c>
       <c r="I8">
-        <v>87.0</v>
+        <v>56.0</v>
       </c>
       <c r="J8">
-        <v>50.34952526960575</v>
+        <v>54.184322654683925</v>
       </c>
       <c r="K8">
-        <v>0.15606553619247826</v>
+        <v>0.129443404039074</v>
       </c>
       <c r="L8">
-        <v>0.2590824246843631</v>
+        <v>0.1397977308012327</v>
       </c>
       <c r="M8">
-        <v>0.23249697382695195</v>
+        <v>0.15358524024185327</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="O8">
-        <v>30.0</v>
+        <v>50.0</v>
       </c>
       <c r="P8">
-        <v>4.681966085774348</v>
+        <v>6.4721702019537</v>
       </c>
       <c r="Q8">
-        <v>55.0314913553801</v>
+        <v>60.65649285663763</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E9">
@@ -598,66 +598,66 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-4</t>
         </is>
       </c>
       <c r="H9">
-        <v>0.5787301755127098</v>
+        <v>0.967577190262213</v>
       </c>
       <c r="I9">
-        <v>87.0</v>
+        <v>56.0</v>
       </c>
       <c r="J9">
-        <v>50.34952526960575</v>
+        <v>54.184322654683925</v>
       </c>
       <c r="K9">
-        <v>0.11860970821515045</v>
+        <v>0.09002251880787042</v>
       </c>
       <c r="L9">
-        <v>0.1969024779281606</v>
+        <v>0.0972235236223598</v>
       </c>
       <c r="M9">
-        <v>0.29449592031762223</v>
+        <v>0.11652236137910156</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="O9">
-        <v>30.0</v>
+        <v>50.0</v>
       </c>
       <c r="P9">
-        <v>3.5582912464545133</v>
+        <v>4.501125940393521</v>
       </c>
       <c r="Q9">
-        <v>53.907816516060265</v>
+        <v>58.685448595077446</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E10">
@@ -665,31 +665,31 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H10">
-        <v>0.5787301755127098</v>
+        <v>0.967577190262213</v>
       </c>
       <c r="I10">
-        <v>87.0</v>
+        <v>56.0</v>
       </c>
       <c r="J10">
-        <v>50.34952526960575</v>
+        <v>54.184322654683925</v>
       </c>
       <c r="K10">
-        <v>0.05684157213428127</v>
+        <v>0.0641710214370617</v>
       </c>
       <c r="L10">
-        <v>0.09436197568474113</v>
+        <v>0.0693041352450102</v>
       </c>
       <c r="M10">
-        <v>0.10349671194639591</v>
+        <v>0.10382622938369798</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -700,31 +700,31 @@
         <v>50.0</v>
       </c>
       <c r="P10">
-        <v>2.8420786067140633</v>
+        <v>3.208551071853085</v>
       </c>
       <c r="Q10">
-        <v>53.19160387631981</v>
+        <v>57.39287372653701</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E11">
@@ -732,31 +732,31 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H11">
-        <v>0.5787301755127098</v>
+        <v>0.967577190262213</v>
       </c>
       <c r="I11">
-        <v>87.0</v>
+        <v>56.0</v>
       </c>
       <c r="J11">
-        <v>50.34952526960575</v>
+        <v>54.184322654683925</v>
       </c>
       <c r="K11">
-        <v>0.04804554216707387</v>
+        <v>0.06144394507410913</v>
       </c>
       <c r="L11">
-        <v>0.07975979747744102</v>
+        <v>0.06635891690737</v>
       </c>
       <c r="M11">
-        <v>0.08350455843285644</v>
+        <v>0.053020760192704644</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -767,31 +767,31 @@
         <v>50.0</v>
       </c>
       <c r="P11">
-        <v>2.402277108353694</v>
+        <v>3.0721972537054563</v>
       </c>
       <c r="Q11">
-        <v>52.75180237795944</v>
+        <v>57.25651990838938</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Curacao</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E12">
@@ -799,66 +799,66 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="H12">
-        <v>0.83241184796472</v>
+        <v>0.41659077539587913</v>
       </c>
       <c r="I12">
-        <v>53.0</v>
+        <v>104.0</v>
       </c>
       <c r="J12">
-        <v>44.11782794213016</v>
+        <v>43.32544064117143</v>
       </c>
       <c r="K12">
-        <v>0.11700137508651391</v>
+        <v>0.20399444088728472</v>
       </c>
       <c r="L12">
-        <v>0.1377424178425806</v>
+        <v>0.6136771916319999</v>
       </c>
       <c r="M12">
-        <v>0.15187696656916913</v>
+        <v>0.7164557132591671</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="O12">
-        <v>50.0</v>
+        <v>20.0</v>
       </c>
       <c r="P12">
-        <v>5.8500687543256955</v>
+        <v>4.079888817745695</v>
       </c>
       <c r="Q12">
-        <v>49.96789669645586</v>
+        <v>47.40532945891713</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Curacao</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E13">
@@ -866,31 +866,31 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="H13">
-        <v>0.83241184796472</v>
+        <v>0.41659077539587913</v>
       </c>
       <c r="I13">
-        <v>53.0</v>
+        <v>104.0</v>
       </c>
       <c r="J13">
-        <v>44.11782794213016</v>
+        <v>43.32544064117143</v>
       </c>
       <c r="K13">
-        <v>0.191361745599665</v>
+        <v>0.11033794683665016</v>
       </c>
       <c r="L13">
-        <v>0.2252847840633018</v>
+        <v>0.33193003226283974</v>
       </c>
       <c r="M13">
-        <v>0.20323846058771922</v>
+        <v>0.23847483160381844</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         <v>30.0</v>
       </c>
       <c r="P13">
-        <v>5.74085236798995</v>
+        <v>3.310138405099505</v>
       </c>
       <c r="Q13">
-        <v>49.858680310120114</v>
+        <v>46.63557904627094</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Curacao</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E14">
@@ -933,66 +933,66 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="H14">
-        <v>0.83241184796472</v>
+        <v>0.41659077539587913</v>
       </c>
       <c r="I14">
-        <v>53.0</v>
+        <v>104.0</v>
       </c>
       <c r="J14">
-        <v>44.11782794213016</v>
+        <v>43.32544064117143</v>
       </c>
       <c r="K14">
-        <v>0.09494717789787879</v>
+        <v>0.015695277867272716</v>
       </c>
       <c r="L14">
-        <v>0.11177863372386049</v>
+        <v>0.047216159428549266</v>
       </c>
       <c r="M14">
-        <v>0.16806666533274442</v>
+        <v>0.04240300882064422</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Mega rare</t>
         </is>
       </c>
       <c r="O14">
-        <v>50.0</v>
+        <v>70.0</v>
       </c>
       <c r="P14">
-        <v>4.74735889489394</v>
+        <v>1.0986694507090902</v>
       </c>
       <c r="Q14">
-        <v>48.865186837024105</v>
+        <v>44.42411009188052</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Curacao</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E15">
@@ -1000,66 +1000,66 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>3-3</t>
         </is>
       </c>
       <c r="H15">
-        <v>0.83241184796472</v>
+        <v>0.41659077539587913</v>
       </c>
       <c r="I15">
-        <v>53.0</v>
+        <v>104.0</v>
       </c>
       <c r="J15">
-        <v>44.11782794213016</v>
+        <v>43.32544064117143</v>
       </c>
       <c r="K15">
-        <v>0.08945006905386778</v>
+        <v>0.002331049692709167</v>
       </c>
       <c r="L15">
-        <v>0.1053070425758246</v>
+        <v>0.007012504962166171</v>
       </c>
       <c r="M15">
-        <v>0.08444597035957126</v>
+        <v>0.0025190639252691944</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Ultra rare</t>
         </is>
       </c>
       <c r="O15">
-        <v>50.0</v>
+        <v>100.0</v>
       </c>
       <c r="P15">
-        <v>4.472503452693389</v>
+        <v>0.2331049692709167</v>
       </c>
       <c r="Q15">
-        <v>48.59033139482355</v>
+        <v>43.55854561044235</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Curacao</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E16">
@@ -1067,66 +1067,66 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>4-4</t>
         </is>
       </c>
       <c r="H16">
-        <v>0.83241184796472</v>
+        <v>0.41659077539587913</v>
       </c>
       <c r="I16">
-        <v>53.0</v>
+        <v>104.0</v>
       </c>
       <c r="J16">
-        <v>44.11782794213016</v>
+        <v>43.32544064117143</v>
       </c>
       <c r="K16">
-        <v>0.06456418768832856</v>
+        <v>5.235825026122445e-05</v>
       </c>
       <c r="L16">
-        <v>0.076009596568046</v>
+        <v>0.0001575095078048101</v>
       </c>
       <c r="M16">
-        <v>0.0799998649296986</v>
+        <v>0.00014145320436088468</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Ultra rare</t>
         </is>
       </c>
       <c r="O16">
-        <v>50.0</v>
+        <v>100.0</v>
       </c>
       <c r="P16">
-        <v>3.2282093844164277</v>
+        <v>0.005235825026122445</v>
       </c>
       <c r="Q16">
-        <v>47.34603732654659</v>
+        <v>43.33067646619755</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E17">
@@ -1134,66 +1134,66 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="H17">
-        <v>0.2302240816304737</v>
+        <v>0.5342294324536083</v>
       </c>
       <c r="I17">
-        <v>145.0</v>
+        <v>93.0</v>
       </c>
       <c r="J17">
-        <v>33.38249183641869</v>
+        <v>49.68333721818557</v>
       </c>
       <c r="K17">
-        <v>0.06291878143878378</v>
+        <v>0.10352455024258637</v>
       </c>
       <c r="L17">
-        <v>0.2793488343963301</v>
+        <v>0.18335666176980728</v>
       </c>
       <c r="M17">
-        <v>0.22783357815782715</v>
+        <v>0.16731593681250792</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="O17">
-        <v>30.0</v>
+        <v>50.0</v>
       </c>
       <c r="P17">
-        <v>1.8875634431635133</v>
+        <v>5.176227512129318</v>
       </c>
       <c r="Q17">
-        <v>35.2700552795822</v>
+        <v>54.85956473031489</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E18">
@@ -1201,66 +1201,66 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="H18">
-        <v>0.2302240816304737</v>
+        <v>0.5342294324536083</v>
       </c>
       <c r="I18">
-        <v>145.0</v>
+        <v>93.0</v>
       </c>
       <c r="J18">
-        <v>33.38249183641869</v>
+        <v>49.68333721818557</v>
       </c>
       <c r="K18">
-        <v>0.03626212977468371</v>
+        <v>0.0516577774196959</v>
       </c>
       <c r="L18">
-        <v>0.16099777290095846</v>
+        <v>0.0914932506340588</v>
       </c>
       <c r="M18">
-        <v>0.14772134667780118</v>
+        <v>0.04638282203687233</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Mega rare</t>
         </is>
       </c>
       <c r="O18">
-        <v>50.0</v>
+        <v>70.0</v>
       </c>
       <c r="P18">
-        <v>1.8131064887341855</v>
+        <v>3.6160444193787127</v>
       </c>
       <c r="Q18">
-        <v>35.19559832515287</v>
+        <v>53.29938163756428</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E19">
@@ -1268,31 +1268,31 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H19">
-        <v>0.2302240816304737</v>
+        <v>0.5342294324536083</v>
       </c>
       <c r="I19">
-        <v>145.0</v>
+        <v>93.0</v>
       </c>
       <c r="J19">
-        <v>33.38249183641869</v>
+        <v>49.68333721818557</v>
       </c>
       <c r="K19">
-        <v>0.02331928551128555</v>
+        <v>0.0698028507130157</v>
       </c>
       <c r="L19">
-        <v>0.1035337156500844</v>
+        <v>0.12363074902294803</v>
       </c>
       <c r="M19">
-        <v>0.05277553991657992</v>
+        <v>0.1002800620238449</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1303,31 +1303,31 @@
         <v>50.0</v>
       </c>
       <c r="P19">
-        <v>1.1659642755642776</v>
+        <v>3.490142535650785</v>
       </c>
       <c r="Q19">
-        <v>34.548456111982965</v>
+        <v>53.173479753836354</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E20">
@@ -1335,66 +1335,66 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="H20">
-        <v>0.2302240816304737</v>
+        <v>0.5342294324536083</v>
       </c>
       <c r="I20">
-        <v>145.0</v>
+        <v>93.0</v>
       </c>
       <c r="J20">
-        <v>33.38249183641869</v>
+        <v>49.68333721818557</v>
       </c>
       <c r="K20">
-        <v>0.05827687186154705</v>
+        <v>0.058152520734398076</v>
       </c>
       <c r="L20">
-        <v>0.25873953459550886</v>
+        <v>0.10299636221913756</v>
       </c>
       <c r="M20">
-        <v>0.39567164812841693</v>
+        <v>0.1096501654811901</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Exact</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="O20">
-        <v>20.0</v>
+        <v>50.0</v>
       </c>
       <c r="P20">
-        <v>1.165537437230941</v>
+        <v>2.9076260367199036</v>
       </c>
       <c r="Q20">
-        <v>34.548029273649625</v>
+        <v>52.590963254905475</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E21">
@@ -1402,45 +1402,45 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H21">
-        <v>0.2302240816304737</v>
+        <v>0.5342294324536083</v>
       </c>
       <c r="I21">
-        <v>145.0</v>
+        <v>93.0</v>
       </c>
       <c r="J21">
-        <v>33.38249183641869</v>
+        <v>49.68333721818557</v>
       </c>
       <c r="K21">
-        <v>0.015020952802584035</v>
+        <v>0.12335681993322553</v>
       </c>
       <c r="L21">
-        <v>0.06669051054344845</v>
+        <v>0.2184824242799857</v>
       </c>
       <c r="M21">
-        <v>0.07138948048180067</v>
+        <v>0.3322812775806211</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="O21">
-        <v>50.0</v>
+        <v>20.0</v>
       </c>
       <c r="P21">
-        <v>0.7510476401292018</v>
+        <v>2.4671363986645107</v>
       </c>
       <c r="Q21">
-        <v>34.13353947654789</v>
+        <v>52.15047361685008</v>
       </c>
     </row>
     <row r="22">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E22">
@@ -1469,31 +1469,31 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="H22">
-        <v>0.5092867836944935</v>
+        <v>0.601854657494651</v>
       </c>
       <c r="I22">
-        <v>96.0</v>
+        <v>68.0</v>
       </c>
       <c r="J22">
-        <v>48.891531234671376</v>
+        <v>40.92611670963626</v>
       </c>
       <c r="K22">
-        <v>0.11055701804772465</v>
+        <v>0.1271037826448879</v>
       </c>
       <c r="L22">
-        <v>0.21694311728211282</v>
+        <v>0.2011708310115651</v>
       </c>
       <c r="M22">
-        <v>0.17955358356768283</v>
+        <v>0.18267357379563975</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1504,10 +1504,10 @@
         <v>50.0</v>
       </c>
       <c r="P22">
-        <v>5.527850902386232</v>
+        <v>6.355189132244394</v>
       </c>
       <c r="Q22">
-        <v>54.41938213705761</v>
+        <v>47.28130584188065</v>
       </c>
     </row>
     <row r="23">
@@ -1518,17 +1518,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E23">
@@ -1536,31 +1536,31 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H23">
-        <v>0.5092867836944935</v>
+        <v>0.601854657494651</v>
       </c>
       <c r="I23">
-        <v>96.0</v>
+        <v>68.0</v>
       </c>
       <c r="J23">
-        <v>48.891531234671376</v>
+        <v>40.92611670963626</v>
       </c>
       <c r="K23">
-        <v>0.09963162213064454</v>
+        <v>0.08108836836797223</v>
       </c>
       <c r="L23">
-        <v>0.1955045013566229</v>
+        <v>0.12834090465688416</v>
       </c>
       <c r="M23">
-        <v>0.18203608413450684</v>
+        <v>0.10359130142697562</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         <v>50.0</v>
       </c>
       <c r="P23">
-        <v>4.981581106532227</v>
+        <v>4.054418418398612</v>
       </c>
       <c r="Q23">
-        <v>53.8731123412036</v>
+        <v>44.98053512803487</v>
       </c>
     </row>
     <row r="24">
@@ -1585,17 +1585,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E24">
@@ -1603,45 +1603,45 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="H24">
-        <v>0.5092867836944935</v>
+        <v>0.601854657494651</v>
       </c>
       <c r="I24">
-        <v>96.0</v>
+        <v>68.0</v>
       </c>
       <c r="J24">
-        <v>48.891531234671376</v>
+        <v>40.92611670963626</v>
       </c>
       <c r="K24">
-        <v>0.09695442895789146</v>
+        <v>0.046570255626209374</v>
       </c>
       <c r="L24">
-        <v>0.19025111588440685</v>
+        <v>0.07370808979713996</v>
       </c>
       <c r="M24">
-        <v>0.29524101233389566</v>
+        <v>0.03718376541853245</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Mega rare</t>
         </is>
       </c>
       <c r="O24">
-        <v>30.0</v>
+        <v>70.0</v>
       </c>
       <c r="P24">
-        <v>2.9086328687367438</v>
+        <v>3.2599178938346562</v>
       </c>
       <c r="Q24">
-        <v>51.80016410340812</v>
+        <v>44.186034603470915</v>
       </c>
     </row>
     <row r="25">
@@ -1652,17 +1652,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E25">
@@ -1670,45 +1670,45 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="H25">
-        <v>0.5092867836944935</v>
+        <v>0.601854657494651</v>
       </c>
       <c r="I25">
-        <v>96.0</v>
+        <v>68.0</v>
       </c>
       <c r="J25">
-        <v>48.891531234671376</v>
+        <v>40.92611670963626</v>
       </c>
       <c r="K25">
-        <v>0.03673263369164942</v>
+        <v>0.06289663617594518</v>
       </c>
       <c r="L25">
-        <v>0.07207947717627859</v>
+        <v>0.09954832424380143</v>
       </c>
       <c r="M25">
-        <v>0.03728548925297283</v>
+        <v>0.10546089646362826</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Mega rare</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="O25">
-        <v>70.0</v>
+        <v>50.0</v>
       </c>
       <c r="P25">
-        <v>2.5712843584154594</v>
+        <v>3.144831808797259</v>
       </c>
       <c r="Q25">
-        <v>51.46281559308684</v>
+        <v>44.07094851843352</v>
       </c>
     </row>
     <row r="26">
@@ -1719,17 +1719,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E26">
@@ -1737,45 +1737,45 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="H26">
-        <v>0.5092867836944935</v>
+        <v>0.601854657494651</v>
       </c>
       <c r="I26">
-        <v>96.0</v>
+        <v>68.0</v>
       </c>
       <c r="J26">
-        <v>48.891531234671376</v>
+        <v>40.92611670963626</v>
       </c>
       <c r="K26">
-        <v>0.031889547849941094</v>
+        <v>0.05694030476929419</v>
       </c>
       <c r="L26">
-        <v>0.0625760177096754</v>
+        <v>0.0901210663453957</v>
       </c>
       <c r="M26">
-        <v>0.03236951108984722</v>
+        <v>0.10002008353291347</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Mega rare</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="O26">
-        <v>70.0</v>
+        <v>50.0</v>
       </c>
       <c r="P26">
-        <v>2.2322683494958766</v>
+        <v>2.8470152384647096</v>
       </c>
       <c r="Q26">
-        <v>51.12379958416725</v>
+        <v>43.77313194810097</v>
       </c>
     </row>
     <row r="27">
@@ -1786,17 +1786,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="E27">
@@ -1804,31 +1804,31 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H27">
-        <v>0.8686669773038992</v>
+        <v>0.7819136367200193</v>
       </c>
       <c r="I27">
-        <v>56.0</v>
+        <v>54.0</v>
       </c>
       <c r="J27">
-        <v>48.645350729018354</v>
+        <v>42.223336382881044</v>
       </c>
       <c r="K27">
-        <v>0.17800937997727778</v>
+        <v>0.15241277060510924</v>
       </c>
       <c r="L27">
-        <v>0.20254170078674147</v>
+        <v>0.19664883172427908</v>
       </c>
       <c r="M27">
-        <v>0.1828398700353069</v>
+        <v>0.183666943842493</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
         <v>50.0</v>
       </c>
       <c r="P27">
-        <v>8.90046899886389</v>
+        <v>7.620638530255462</v>
       </c>
       <c r="Q27">
-        <v>57.54581972788225</v>
+        <v>49.843974913136506</v>
       </c>
     </row>
     <row r="28">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="E28">
@@ -1871,31 +1871,31 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H28">
-        <v>0.8686669773038992</v>
+        <v>0.7819136367200193</v>
       </c>
       <c r="I28">
-        <v>56.0</v>
+        <v>54.0</v>
       </c>
       <c r="J28">
-        <v>48.645350729018354</v>
+        <v>42.223336382881044</v>
       </c>
       <c r="K28">
-        <v>0.12002009852278538</v>
+        <v>0.11376227686700376</v>
       </c>
       <c r="L28">
-        <v>0.13656064015559286</v>
+        <v>0.14678047483404472</v>
       </c>
       <c r="M28">
-        <v>0.15067186746729072</v>
+        <v>0.12185837845343732</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -1906,10 +1906,10 @@
         <v>50.0</v>
       </c>
       <c r="P28">
-        <v>6.001004926139268</v>
+        <v>5.688113843350187</v>
       </c>
       <c r="Q28">
-        <v>54.64635565515762</v>
+        <v>47.91145022623123</v>
       </c>
     </row>
     <row r="29">
@@ -1920,17 +1920,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="E29">
@@ -1938,45 +1938,45 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="H29">
-        <v>0.8686669773038992</v>
+        <v>0.7819136367200193</v>
       </c>
       <c r="I29">
-        <v>56.0</v>
+        <v>54.0</v>
       </c>
       <c r="J29">
-        <v>48.645350729018354</v>
+        <v>42.223336382881044</v>
       </c>
       <c r="K29">
-        <v>0.0864245050353621</v>
+        <v>0.06511248206229041</v>
       </c>
       <c r="L29">
-        <v>0.0983350778579698</v>
+        <v>0.08401063426235135</v>
       </c>
       <c r="M29">
-        <v>0.147949556277581</v>
+        <v>0.04359145722391589</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Mega rare</t>
         </is>
       </c>
       <c r="O29">
-        <v>50.0</v>
+        <v>70.0</v>
       </c>
       <c r="P29">
-        <v>4.321225251768105</v>
+        <v>4.557873744360329</v>
       </c>
       <c r="Q29">
-        <v>52.96657598078646</v>
+        <v>46.78121012724137</v>
       </c>
     </row>
     <row r="30">
@@ -1987,17 +1987,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="E30">
@@ -2005,31 +2005,31 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H30">
-        <v>0.8686669773038992</v>
+        <v>0.7819136367200193</v>
       </c>
       <c r="I30">
-        <v>56.0</v>
+        <v>54.0</v>
       </c>
       <c r="J30">
-        <v>48.645350729018354</v>
+        <v>42.223336382881044</v>
       </c>
       <c r="K30">
-        <v>0.07545589839142147</v>
+        <v>0.08956929318582713</v>
       </c>
       <c r="L30">
-        <v>0.08585483527070802</v>
+        <v>0.1155657547161726</v>
       </c>
       <c r="M30">
-        <v>0.06889198339271474</v>
+        <v>0.1798943561428575</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2040,10 +2040,10 @@
         <v>50.0</v>
       </c>
       <c r="P30">
-        <v>3.7727949195710737</v>
+        <v>4.478464659291356</v>
       </c>
       <c r="Q30">
-        <v>52.41814564858943</v>
+        <v>46.7018010421724</v>
       </c>
     </row>
     <row r="31">
@@ -2054,17 +2054,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="E31">
@@ -2072,31 +2072,31 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0-4</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="H31">
-        <v>0.8686669773038992</v>
+        <v>0.7819136367200193</v>
       </c>
       <c r="I31">
-        <v>56.0</v>
+        <v>54.0</v>
       </c>
       <c r="J31">
-        <v>48.645350729018354</v>
+        <v>42.223336382881044</v>
       </c>
       <c r="K31">
-        <v>0.07252791449382026</v>
+        <v>0.08298528118487213</v>
       </c>
       <c r="L31">
-        <v>0.08252333196132039</v>
+        <v>0.10707080863713957</v>
       </c>
       <c r="M31">
-        <v>0.09932805759392878</v>
+        <v>0.12222523677339636</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2107,31 +2107,31 @@
         <v>50.0</v>
       </c>
       <c r="P31">
-        <v>3.626395724691013</v>
+        <v>4.149264059243606</v>
       </c>
       <c r="Q31">
-        <v>52.27174645370937</v>
+        <v>46.37260044212465</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="E32">
@@ -2139,66 +2139,66 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H32">
-        <v>0.42365979699675355</v>
+        <v>0.35974963348128647</v>
       </c>
       <c r="I32">
-        <v>104.0</v>
+        <v>99.0</v>
       </c>
       <c r="J32">
-        <v>44.06061888766237</v>
+        <v>35.61521371464736</v>
       </c>
       <c r="K32">
-        <v>0.19599781826859305</v>
+        <v>0.06984278471064481</v>
       </c>
       <c r="L32">
-        <v>0.5979923887354501</v>
+        <v>0.19432749977103153</v>
       </c>
       <c r="M32">
-        <v>0.7028209774258994</v>
+        <v>0.17910976396301648</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Exact</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="O32">
-        <v>20.0</v>
+        <v>50.0</v>
       </c>
       <c r="P32">
-        <v>3.919956365371861</v>
+        <v>3.4921392355322407</v>
       </c>
       <c r="Q32">
-        <v>47.98057525303423</v>
+        <v>39.1073529501796</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="E33">
@@ -2206,31 +2206,31 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H33">
-        <v>0.42365979699675355</v>
+        <v>0.35974963348128647</v>
       </c>
       <c r="I33">
-        <v>104.0</v>
+        <v>99.0</v>
       </c>
       <c r="J33">
-        <v>44.06061888766237</v>
+        <v>35.61521371464736</v>
       </c>
       <c r="K33">
-        <v>0.11216302304734327</v>
+        <v>0.1040572278784683</v>
       </c>
       <c r="L33">
-        <v>0.34221112598281384</v>
+        <v>0.2895242652552096</v>
       </c>
       <c r="M33">
-        <v>0.24750832961949393</v>
+        <v>0.2372015071808707</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2241,31 +2241,31 @@
         <v>30.0</v>
       </c>
       <c r="P33">
-        <v>3.364890691420298</v>
+        <v>3.121716836354049</v>
       </c>
       <c r="Q33">
-        <v>47.42550957908267</v>
+        <v>38.73693055100141</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="E34">
@@ -2273,66 +2273,66 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H34">
-        <v>0.42365979699675355</v>
+        <v>0.3557415440455039</v>
       </c>
       <c r="I34">
-        <v>104.0</v>
+        <v>94.0</v>
       </c>
       <c r="J34">
-        <v>44.06061888766237</v>
+        <v>33.43970514027737</v>
       </c>
       <c r="K34">
-        <v>0.016880516061425044</v>
+        <v>0.08800940016437485</v>
       </c>
       <c r="L34">
-        <v>0.051502716774252166</v>
+        <v>0.22357059783171607</v>
       </c>
       <c r="M34">
-        <v>0.04656245235690126</v>
+        <v>0.17641241087980752</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Mega rare</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="O34">
-        <v>70.0</v>
+        <v>50.0</v>
       </c>
       <c r="P34">
-        <v>1.181636124299753</v>
+        <v>4.4004700082187425</v>
       </c>
       <c r="Q34">
-        <v>45.24225501196212</v>
+        <v>37.84017514849611</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="E35">
@@ -2340,66 +2340,66 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3-3</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="H35">
-        <v>0.42365979699675355</v>
+        <v>0.3557415440455039</v>
       </c>
       <c r="I35">
-        <v>104.0</v>
+        <v>94.0</v>
       </c>
       <c r="J35">
-        <v>44.06061888766237</v>
+        <v>33.43970514027737</v>
       </c>
       <c r="K35">
-        <v>0.0026525290294611885</v>
+        <v>0.0851643545604238</v>
       </c>
       <c r="L35">
-        <v>0.008092907280957193</v>
+        <v>0.21634331818493008</v>
       </c>
       <c r="M35">
-        <v>0.002926646462943684</v>
+        <v>0.19204829502402665</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Ultra rare</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="O35">
-        <v>100.0</v>
+        <v>50.0</v>
       </c>
       <c r="P35">
-        <v>0.26525290294611886</v>
+        <v>4.25821772802119</v>
       </c>
       <c r="Q35">
-        <v>44.32587179060849</v>
+        <v>37.69792286829856</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="E36">
@@ -2407,66 +2407,66 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="H36">
-        <v>0.42365979699675355</v>
+        <v>0.35974963348128647</v>
       </c>
       <c r="I36">
-        <v>104.0</v>
+        <v>99.0</v>
       </c>
       <c r="J36">
-        <v>44.06061888766237</v>
+        <v>35.61521371464736</v>
       </c>
       <c r="K36">
-        <v>6.303556377669003e-05</v>
+        <v>0.026208521057807483</v>
       </c>
       <c r="L36">
-        <v>0.0001923224844597617</v>
+        <v>0.0729214390714854</v>
       </c>
       <c r="M36">
-        <v>0.00017387444936293976</v>
+        <v>0.03733943344590514</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Ultra rare</t>
+          <t>Mega rare</t>
         </is>
       </c>
       <c r="O36">
-        <v>100.0</v>
+        <v>70.0</v>
       </c>
       <c r="P36">
-        <v>0.006303556377669003</v>
+        <v>1.8345964740465237</v>
       </c>
       <c r="Q36">
-        <v>44.06692244404004</v>
+        <v>37.44981018869388</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E37">
@@ -2474,31 +2474,31 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H37">
-        <v>0.49848177273002836</v>
+        <v>0.6445013457785898</v>
       </c>
       <c r="I37">
-        <v>93.0</v>
+        <v>57.0</v>
       </c>
       <c r="J37">
-        <v>46.35880486389264</v>
+        <v>36.73657670937962</v>
       </c>
       <c r="K37">
-        <v>0.10862993001185103</v>
+        <v>0.11798468405201236</v>
       </c>
       <c r="L37">
-        <v>0.20524834697477426</v>
+        <v>0.17628370809713498</v>
       </c>
       <c r="M37">
-        <v>0.18489142906938963</v>
+        <v>0.14094841706300779</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -2509,31 +2509,31 @@
         <v>50.0</v>
       </c>
       <c r="P37">
-        <v>5.4314965005925515</v>
+        <v>5.899234202600618</v>
       </c>
       <c r="Q37">
-        <v>51.79030136448519</v>
+        <v>42.635810911980236</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E38">
@@ -2541,66 +2541,66 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="H38">
-        <v>0.49848177273002836</v>
+        <v>0.6445013457785898</v>
       </c>
       <c r="I38">
-        <v>93.0</v>
+        <v>57.0</v>
       </c>
       <c r="J38">
-        <v>46.35880486389264</v>
+        <v>36.73657670937962</v>
       </c>
       <c r="K38">
-        <v>0.08285645576608425</v>
+        <v>0.17145015217525797</v>
       </c>
       <c r="L38">
-        <v>0.1565512431088007</v>
+        <v>0.25616772907531504</v>
       </c>
       <c r="M38">
-        <v>0.12535484066597852</v>
+        <v>0.23042254354487987</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="O38">
-        <v>50.0</v>
+        <v>30.0</v>
       </c>
       <c r="P38">
-        <v>4.142822788304212</v>
+        <v>5.143504565257739</v>
       </c>
       <c r="Q38">
-        <v>50.501627652196845</v>
+        <v>41.88008127463736</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E39">
@@ -2608,66 +2608,66 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H39">
-        <v>0.49848177273002836</v>
+        <v>0.6445013457785898</v>
       </c>
       <c r="I39">
-        <v>93.0</v>
+        <v>57.0</v>
       </c>
       <c r="J39">
-        <v>46.35880486389264</v>
+        <v>36.73657670937962</v>
       </c>
       <c r="K39">
-        <v>0.042596746662092</v>
+        <v>0.1198501751592163</v>
       </c>
       <c r="L39">
-        <v>0.08048345274588507</v>
+        <v>0.17907098250010042</v>
       </c>
       <c r="M39">
-        <v>0.040278306781779044</v>
+        <v>0.268456864907071</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Mega rare</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="O39">
-        <v>70.0</v>
+        <v>30.0</v>
       </c>
       <c r="P39">
-        <v>2.98177226634644</v>
+        <v>3.595505254776489</v>
       </c>
       <c r="Q39">
-        <v>49.340577130239076</v>
+        <v>40.33208196415611</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E40">
@@ -2675,31 +2675,31 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="H40">
-        <v>0.49848177273002836</v>
+        <v>0.6445013457785898</v>
       </c>
       <c r="I40">
-        <v>93.0</v>
+        <v>57.0</v>
       </c>
       <c r="J40">
-        <v>46.35880486389264</v>
+        <v>36.73657670937962</v>
       </c>
       <c r="K40">
-        <v>0.050859074499127306</v>
+        <v>0.0712051677867319</v>
       </c>
       <c r="L40">
-        <v>0.09609451988484163</v>
+        <v>0.1063893259873477</v>
       </c>
       <c r="M40">
-        <v>0.10099096499747706</v>
+        <v>0.11696307600827545</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -2710,31 +2710,31 @@
         <v>50.0</v>
       </c>
       <c r="P40">
-        <v>2.5429537249563654</v>
+        <v>3.560258389336595</v>
       </c>
       <c r="Q40">
-        <v>48.901758588849</v>
+        <v>40.296835098716215</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E41">
@@ -2742,66 +2742,66 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="H41">
-        <v>0.49848177273002836</v>
+        <v>0.6445013457785898</v>
       </c>
       <c r="I41">
-        <v>93.0</v>
+        <v>57.0</v>
       </c>
       <c r="J41">
-        <v>46.35880486389264</v>
+        <v>36.73657670937962</v>
       </c>
       <c r="K41">
-        <v>0.12204222548438791</v>
+        <v>0.05535872778091479</v>
       </c>
       <c r="L41">
-        <v>0.23058990316076386</v>
+        <v>0.08271278502943188</v>
       </c>
       <c r="M41">
-        <v>0.34619926991507566</v>
+        <v>0.0868000513131989</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Exact</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="O41">
-        <v>20.0</v>
+        <v>50.0</v>
       </c>
       <c r="P41">
-        <v>2.440844509687758</v>
+        <v>2.7679363890457394</v>
       </c>
       <c r="Q41">
-        <v>48.799649373580394</v>
+        <v>39.504513098425356</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E42">
@@ -2809,66 +2809,66 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="H42">
-        <v>0.5757235518344145</v>
+        <v>0.35803721611275724</v>
       </c>
       <c r="I42">
-        <v>68.0</v>
+        <v>114.0</v>
       </c>
       <c r="J42">
-        <v>39.149201524740185</v>
+        <v>40.81624263685433</v>
       </c>
       <c r="K42">
-        <v>0.12557164972555723</v>
+        <v>0.11422948109528094</v>
       </c>
       <c r="L42">
-        <v>0.20875554283067355</v>
+        <v>0.3856892967144294</v>
       </c>
       <c r="M42">
-        <v>0.18873285011769897</v>
+        <v>0.28808577842058697</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="O42">
-        <v>50.0</v>
+        <v>30.0</v>
       </c>
       <c r="P42">
-        <v>6.278582486277862</v>
+        <v>3.4268844328584285</v>
       </c>
       <c r="Q42">
-        <v>45.42778401101805</v>
+        <v>44.243127069712756</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E43">
@@ -2876,66 +2876,66 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="H43">
-        <v>0.5757235518344145</v>
+        <v>0.35803721611275724</v>
       </c>
       <c r="I43">
-        <v>68.0</v>
+        <v>114.0</v>
       </c>
       <c r="J43">
-        <v>39.149201524740185</v>
+        <v>40.81624263685433</v>
       </c>
       <c r="K43">
-        <v>0.08581220086929404</v>
+        <v>0.15522079201140002</v>
       </c>
       <c r="L43">
-        <v>0.1426577783529616</v>
+        <v>0.524094108913945</v>
       </c>
       <c r="M43">
-        <v>0.11464428674133627</v>
+        <v>0.6361314625651947</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="O43">
-        <v>50.0</v>
+        <v>20.0</v>
       </c>
       <c r="P43">
-        <v>4.290610043464702</v>
+        <v>3.1044158402280004</v>
       </c>
       <c r="Q43">
-        <v>43.43981156820489</v>
+        <v>43.92065847708233</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E44">
@@ -2943,66 +2943,66 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="H44">
-        <v>0.5757235518344145</v>
+        <v>0.35803721611275724</v>
       </c>
       <c r="I44">
-        <v>68.0</v>
+        <v>114.0</v>
       </c>
       <c r="J44">
-        <v>39.149201524740185</v>
+        <v>40.81624263685433</v>
       </c>
       <c r="K44">
-        <v>0.04377653689803711</v>
+        <v>0.0221077251868116</v>
       </c>
       <c r="L44">
-        <v>0.07277593902261838</v>
+        <v>0.07464546715523424</v>
       </c>
       <c r="M44">
-        <v>0.036553148895499106</v>
+        <v>0.0696943682848235</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Mega rare</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="O44">
-        <v>70.0</v>
+        <v>50.0</v>
       </c>
       <c r="P44">
-        <v>3.0643575828625975</v>
+        <v>1.1053862593405799</v>
       </c>
       <c r="Q44">
-        <v>42.213559107602784</v>
+        <v>41.9216288961949</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E45">
@@ -3010,66 +3010,66 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>3-3</t>
         </is>
       </c>
       <c r="H45">
-        <v>0.5757235518344145</v>
+        <v>0.35803721611275724</v>
       </c>
       <c r="I45">
-        <v>68.0</v>
+        <v>114.0</v>
       </c>
       <c r="J45">
-        <v>39.149201524740185</v>
+        <v>40.81624263685433</v>
       </c>
       <c r="K45">
-        <v>0.05856412978406112</v>
+        <v>0.0044673329681555705</v>
       </c>
       <c r="L45">
-        <v>0.09735944960663727</v>
+        <v>0.015083693755379296</v>
       </c>
       <c r="M45">
-        <v>0.10269147278434043</v>
+        <v>0.005633287848526418</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Mega rare</t>
         </is>
       </c>
       <c r="O45">
-        <v>50.0</v>
+        <v>70.0</v>
       </c>
       <c r="P45">
-        <v>2.928206489203056</v>
+        <v>0.31271330777088996</v>
       </c>
       <c r="Q45">
-        <v>42.07740801394324</v>
+        <v>41.12895594462522</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E46">
@@ -3077,66 +3077,66 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>4-4</t>
         </is>
       </c>
       <c r="H46">
-        <v>0.5757235518344145</v>
+        <v>0.35803721611275724</v>
       </c>
       <c r="I46">
-        <v>68.0</v>
+        <v>114.0</v>
       </c>
       <c r="J46">
-        <v>39.149201524740185</v>
+        <v>40.81624263685433</v>
       </c>
       <c r="K46">
-        <v>0.052516473740974054</v>
+        <v>0.0001365223197855764</v>
       </c>
       <c r="L46">
-        <v>0.08730557420652062</v>
+        <v>0.0004609597890057883</v>
       </c>
       <c r="M46">
-        <v>0.09647207760863859</v>
+        <v>0.0004303851596595067</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Ultra rare</t>
         </is>
       </c>
       <c r="O46">
-        <v>50.0</v>
+        <v>100.0</v>
       </c>
       <c r="P46">
-        <v>2.625823687048703</v>
+        <v>0.013652231978557638</v>
       </c>
       <c r="Q46">
-        <v>41.775025211788886</v>
+        <v>40.82989486883288</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E47">
@@ -3144,31 +3144,31 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="H47">
-        <v>0.7822789687594077</v>
+        <v>0.823908906197839</v>
       </c>
       <c r="I47">
-        <v>54.0</v>
+        <v>32.0</v>
       </c>
       <c r="J47">
-        <v>42.24306431300802</v>
+        <v>26.365084998330847</v>
       </c>
       <c r="K47">
-        <v>0.14685633643969787</v>
+        <v>0.16314093671736557</v>
       </c>
       <c r="L47">
-        <v>0.18940958962564491</v>
+        <v>0.1929486708826308</v>
       </c>
       <c r="M47">
-        <v>0.177196773204457</v>
+        <v>0.17515365773852304</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -3179,31 +3179,31 @@
         <v>50.0</v>
       </c>
       <c r="P47">
-        <v>7.3428168219848935</v>
+        <v>8.157046835868279</v>
       </c>
       <c r="Q47">
-        <v>49.58588113499292</v>
+        <v>34.52213183419913</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E48">
@@ -3211,31 +3211,31 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="H48">
-        <v>0.7822789687594077</v>
+        <v>0.823908906197839</v>
       </c>
       <c r="I48">
-        <v>54.0</v>
+        <v>32.0</v>
       </c>
       <c r="J48">
-        <v>42.24306431300802</v>
+        <v>26.365084998330847</v>
       </c>
       <c r="K48">
-        <v>0.10776506757464871</v>
+        <v>0.10509140337959356</v>
       </c>
       <c r="L48">
-        <v>0.13899119180108085</v>
+        <v>0.12429281706536</v>
       </c>
       <c r="M48">
-        <v>0.11558157343174968</v>
+        <v>0.13790297229505274</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -3246,31 +3246,31 @@
         <v>50.0</v>
       </c>
       <c r="P48">
-        <v>5.388253378732435</v>
+        <v>5.254570168979678</v>
       </c>
       <c r="Q48">
-        <v>47.631317691740456</v>
+        <v>31.619655167310526</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E49">
@@ -3278,66 +3278,66 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H49">
-        <v>0.7822789687594077</v>
+        <v>0.823908906197839</v>
       </c>
       <c r="I49">
-        <v>54.0</v>
+        <v>32.0</v>
       </c>
       <c r="J49">
-        <v>42.24306431300802</v>
+        <v>26.365084998330847</v>
       </c>
       <c r="K49">
-        <v>0.06765895457416013</v>
+        <v>0.09914547504064475</v>
       </c>
       <c r="L49">
-        <v>0.08726388749084736</v>
+        <v>0.11726049891610775</v>
       </c>
       <c r="M49">
-        <v>0.045354031473439395</v>
+        <v>0.17740992288646779</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Mega rare</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="O49">
-        <v>70.0</v>
+        <v>50.0</v>
       </c>
       <c r="P49">
-        <v>4.736126820191209</v>
+        <v>4.957273752032237</v>
       </c>
       <c r="Q49">
-        <v>46.97919113319923</v>
+        <v>31.322358750363083</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E50">
@@ -3345,31 +3345,31 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H50">
-        <v>0.7822789687594077</v>
+        <v>0.823908906197839</v>
       </c>
       <c r="I50">
-        <v>54.0</v>
+        <v>32.0</v>
       </c>
       <c r="J50">
-        <v>42.24306431300802</v>
+        <v>26.365084998330847</v>
       </c>
       <c r="K50">
-        <v>0.08995741672682797</v>
+        <v>0.07238025515970717</v>
       </c>
       <c r="L50">
-        <v>0.11602357650402155</v>
+        <v>0.08560496410172075</v>
       </c>
       <c r="M50">
-        <v>0.18090428097108258</v>
+        <v>0.0690754697236418</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -3380,31 +3380,31 @@
         <v>50.0</v>
       </c>
       <c r="P50">
-        <v>4.497870836341399</v>
+        <v>3.6190127579853586</v>
       </c>
       <c r="Q50">
-        <v>46.74093514934942</v>
+        <v>29.984097756316206</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E51">
@@ -3412,31 +3412,31 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="H51">
-        <v>0.7822789687594077</v>
+        <v>0.823908906197839</v>
       </c>
       <c r="I51">
-        <v>54.0</v>
+        <v>32.0</v>
       </c>
       <c r="J51">
-        <v>42.24306431300802</v>
+        <v>26.365084998330847</v>
       </c>
       <c r="K51">
-        <v>0.08133247788758266</v>
+        <v>0.07103149028744953</v>
       </c>
       <c r="L51">
-        <v>0.10489946592293982</v>
+        <v>0.0840097643028735</v>
       </c>
       <c r="M51">
-        <v>0.11994366048536392</v>
+        <v>0.08897212753752871</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -3447,10 +3447,10 @@
         <v>50.0</v>
       </c>
       <c r="P51">
-        <v>4.066623894379133</v>
+        <v>3.551574514372476</v>
       </c>
       <c r="Q51">
-        <v>46.309688207387154</v>
+        <v>29.916659512703323</v>
       </c>
     </row>
     <row r="52">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="E52">
@@ -3479,45 +3479,45 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="H52">
-        <v>0.3902397571571887</v>
+        <v>0.2915603221397827</v>
       </c>
       <c r="I52">
-        <v>99.0</v>
+        <v>120.0</v>
       </c>
       <c r="J52">
-        <v>38.63373595856169</v>
+        <v>34.987238656773926</v>
       </c>
       <c r="K52">
-        <v>0.07605913920936136</v>
+        <v>0.10705747284405816</v>
       </c>
       <c r="L52">
-        <v>0.1974645238162894</v>
+        <v>0.43550553763499267</v>
       </c>
       <c r="M52">
-        <v>0.18224656014232318</v>
+        <v>0.5506666335470126</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="O52">
-        <v>50.0</v>
+        <v>20.0</v>
       </c>
       <c r="P52">
-        <v>3.8029569604680677</v>
+        <v>2.141149456881163</v>
       </c>
       <c r="Q52">
-        <v>42.43669291902975</v>
+        <v>37.12838811365509</v>
       </c>
     </row>
     <row r="53">
@@ -3528,17 +3528,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="E53">
@@ -3546,45 +3546,45 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="H53">
-        <v>0.3902397571571887</v>
+        <v>0.2915603221397827</v>
       </c>
       <c r="I53">
-        <v>99.0</v>
+        <v>120.0</v>
       </c>
       <c r="J53">
-        <v>38.63373595856169</v>
+        <v>34.987238656773926</v>
       </c>
       <c r="K53">
-        <v>0.10845605509827161</v>
+        <v>0.10446322900726727</v>
       </c>
       <c r="L53">
-        <v>0.2815733059510821</v>
+        <v>0.4249522569822392</v>
       </c>
       <c r="M53">
-        <v>0.23099852940438115</v>
+        <v>0.3306601476971223</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="O53">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
       <c r="P53">
-        <v>3.2536816529481483</v>
+        <v>2.0892645801453456</v>
       </c>
       <c r="Q53">
-        <v>41.88741761150983</v>
+        <v>37.07650323691927</v>
       </c>
     </row>
     <row r="54">
@@ -3595,17 +3595,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="E54">
@@ -3613,45 +3613,45 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="H54">
-        <v>0.3902397571571887</v>
+        <v>0.2915603221397827</v>
       </c>
       <c r="I54">
-        <v>99.0</v>
+        <v>120.0</v>
       </c>
       <c r="J54">
-        <v>38.63373595856169</v>
+        <v>34.987238656773926</v>
       </c>
       <c r="K54">
-        <v>0.027428851445557907</v>
+        <v>0.026806952764561305</v>
       </c>
       <c r="L54">
-        <v>0.07121070716585502</v>
+        <v>0.10904961667731054</v>
       </c>
       <c r="M54">
-        <v>0.036512624522404856</v>
+        <v>0.10606592200762545</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Mega rare</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="O54">
-        <v>70.0</v>
+        <v>50.0</v>
       </c>
       <c r="P54">
-        <v>1.9200196011890536</v>
+        <v>1.3403476382280652</v>
       </c>
       <c r="Q54">
-        <v>40.55375555975074</v>
+        <v>36.32758629500199</v>
       </c>
     </row>
     <row r="55">
@@ -3662,17 +3662,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="E55">
@@ -3680,45 +3680,45 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>3-3</t>
         </is>
       </c>
       <c r="H55">
-        <v>0.3902397571571887</v>
+        <v>0.2915603221397827</v>
       </c>
       <c r="I55">
-        <v>99.0</v>
+        <v>120.0</v>
       </c>
       <c r="J55">
-        <v>38.63373595856169</v>
+        <v>34.987238656773926</v>
       </c>
       <c r="K55">
-        <v>0.08298109734724717</v>
+        <v>0.007182404576603638</v>
       </c>
       <c r="L55">
-        <v>0.21543529211293716</v>
+        <v>0.029217735890348047</v>
       </c>
       <c r="M55">
-        <v>0.3313872973402806</v>
+        <v>0.011367325041977341</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Exact</t>
+          <t>Mega rare</t>
         </is>
       </c>
       <c r="O55">
-        <v>20.0</v>
+        <v>70.0</v>
       </c>
       <c r="P55">
-        <v>1.6596219469449434</v>
+        <v>0.5027683203622546</v>
       </c>
       <c r="Q55">
-        <v>40.29335790550663</v>
+        <v>35.49000697713618</v>
       </c>
     </row>
     <row r="56">
@@ -3729,17 +3729,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="E56">
@@ -3747,45 +3747,45 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H56">
-        <v>0.3902397571571887</v>
+        <v>0.5375950650559634</v>
       </c>
       <c r="I56">
-        <v>99.0</v>
+        <v>57.0</v>
       </c>
       <c r="J56">
-        <v>38.63373595856169</v>
+        <v>30.642918708189917</v>
       </c>
       <c r="K56">
-        <v>0.02602585588858541</v>
+        <v>0.1518453434585705</v>
       </c>
       <c r="L56">
-        <v>0.06756825403722633</v>
+        <v>0.28427978144652943</v>
       </c>
       <c r="M56">
-        <v>0.07275448052291204</v>
+        <v>0.23471107415825404</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="O56">
-        <v>50.0</v>
+        <v>30.0</v>
       </c>
       <c r="P56">
-        <v>1.3012927944292705</v>
+        <v>4.555360303757115</v>
       </c>
       <c r="Q56">
-        <v>39.93502875299096</v>
+        <v>35.19827901194703</v>
       </c>
     </row>
     <row r="57">
@@ -3796,17 +3796,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E57">
@@ -3814,31 +3814,31 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>England</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="H57">
-        <v>0.6376857765387572</v>
+        <v>0.8215739203464419</v>
       </c>
       <c r="I57">
-        <v>57.0</v>
+        <v>32.0</v>
       </c>
       <c r="J57">
-        <v>36.348089262709166</v>
+        <v>26.290365451086142</v>
       </c>
       <c r="K57">
-        <v>0.10874930003165895</v>
+        <v>0.16847400263670353</v>
       </c>
       <c r="L57">
-        <v>0.16347657606575292</v>
+        <v>0.20053483435690786</v>
       </c>
       <c r="M57">
-        <v>0.13077830149200367</v>
+        <v>0.18179064602333886</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -3849,10 +3849,10 @@
         <v>50.0</v>
       </c>
       <c r="P57">
-        <v>5.4374650015829475</v>
+        <v>8.423700131835176</v>
       </c>
       <c r="Q57">
-        <v>41.78555426429212</v>
+        <v>34.71406558292132</v>
       </c>
     </row>
     <row r="58">
@@ -3863,17 +3863,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E58">
@@ -3881,45 +3881,45 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>England</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="H58">
-        <v>0.6376857765387572</v>
+        <v>0.8215739203464419</v>
       </c>
       <c r="I58">
-        <v>57.0</v>
+        <v>32.0</v>
       </c>
       <c r="J58">
-        <v>36.348089262709166</v>
+        <v>26.290365451086142</v>
       </c>
       <c r="K58">
-        <v>0.16191113687690886</v>
+        <v>0.10595006984088923</v>
       </c>
       <c r="L58">
-        <v>0.24339171172453522</v>
+        <v>0.1261125121569158</v>
       </c>
       <c r="M58">
-        <v>0.21904758376046402</v>
+        <v>0.13973012964261022</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="O58">
-        <v>30.0</v>
+        <v>50.0</v>
       </c>
       <c r="P58">
-        <v>4.857334106307266</v>
+        <v>5.297503492044461</v>
       </c>
       <c r="Q58">
-        <v>41.20542336901643</v>
+        <v>31.5878689431306</v>
       </c>
     </row>
     <row r="59">
@@ -3930,17 +3930,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E59">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>England</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3957,36 +3957,36 @@
         </is>
       </c>
       <c r="H59">
-        <v>0.6376857765387572</v>
+        <v>0.8215739203464419</v>
       </c>
       <c r="I59">
-        <v>57.0</v>
+        <v>32.0</v>
       </c>
       <c r="J59">
-        <v>36.348089262709166</v>
+        <v>26.290365451086142</v>
       </c>
       <c r="K59">
-        <v>0.1225893881994201</v>
+        <v>0.10047018781765425</v>
       </c>
       <c r="L59">
-        <v>0.18428158561942423</v>
+        <v>0.11958980113547411</v>
       </c>
       <c r="M59">
-        <v>0.27641612345430294</v>
+        <v>0.18068604120525267</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="O59">
-        <v>30.0</v>
+        <v>50.0</v>
       </c>
       <c r="P59">
-        <v>3.677681645982603</v>
+        <v>5.023509390882713</v>
       </c>
       <c r="Q59">
-        <v>40.02577090869177</v>
+        <v>31.313874841968854</v>
       </c>
     </row>
     <row r="60">
@@ -3997,17 +3997,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E60">
@@ -4015,31 +4015,31 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>England</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H60">
-        <v>0.6376857765387572</v>
+        <v>0.8215739203464419</v>
       </c>
       <c r="I60">
-        <v>57.0</v>
+        <v>32.0</v>
       </c>
       <c r="J60">
-        <v>36.348089262709166</v>
+        <v>26.290365451086142</v>
       </c>
       <c r="K60">
-        <v>0.06889510595514907</v>
+        <v>0.07656423347498763</v>
       </c>
       <c r="L60">
-        <v>0.10356605537650579</v>
+        <v>0.09113451118437015</v>
       </c>
       <c r="M60">
-        <v>0.11392008303540062</v>
+        <v>0.07343651442617927</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -4050,10 +4050,10 @@
         <v>50.0</v>
       </c>
       <c r="P60">
-        <v>3.4447552977574536</v>
+        <v>3.828211673749381</v>
       </c>
       <c r="Q60">
-        <v>39.79284456046662</v>
+        <v>30.118577124835525</v>
       </c>
     </row>
     <row r="61">
@@ -4064,17 +4064,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E61">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>England</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4091,22 +4091,22 @@
         </is>
       </c>
       <c r="H61">
-        <v>0.6376857765387572</v>
+        <v>0.8215739203464419</v>
       </c>
       <c r="I61">
-        <v>57.0</v>
+        <v>32.0</v>
       </c>
       <c r="J61">
-        <v>36.348089262709166</v>
+        <v>26.290365451086142</v>
       </c>
       <c r="K61">
-        <v>0.05801473547398783</v>
+        <v>0.07027152135950115</v>
       </c>
       <c r="L61">
-        <v>0.08721021941186677</v>
+        <v>0.08364428739918496</v>
       </c>
       <c r="M61">
-        <v>0.09156865829040566</v>
+        <v>0.0884636357888969</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -4117,31 +4117,31 @@
         <v>50.0</v>
       </c>
       <c r="P61">
-        <v>2.900736773699392</v>
+        <v>3.5135760679750576</v>
       </c>
       <c r="Q61">
-        <v>39.24882603640856</v>
+        <v>29.8039415190612</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E62">
@@ -4149,31 +4149,31 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H62">
-        <v>0.3594893413388667</v>
+        <v>0.22695912423809647</v>
       </c>
       <c r="I62">
-        <v>114.0</v>
+        <v>154.0</v>
       </c>
       <c r="J62">
-        <v>40.9817849126308</v>
+        <v>34.95170513266686</v>
       </c>
       <c r="K62">
-        <v>0.11446841917084026</v>
+        <v>0.07557005895308785</v>
       </c>
       <c r="L62">
-        <v>0.3863459266482994</v>
+        <v>0.33818047161165654</v>
       </c>
       <c r="M62">
-        <v>0.2887365965232233</v>
+        <v>0.2748971861862285</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -4184,31 +4184,31 @@
         <v>30.0</v>
       </c>
       <c r="P62">
-        <v>3.434052575125208</v>
+        <v>2.2671017685926356</v>
       </c>
       <c r="Q62">
-        <v>44.41583748775601</v>
+        <v>37.2188069012595</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E63">
@@ -4216,66 +4216,66 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H63">
-        <v>0.3594893413388667</v>
+        <v>0.22695912423809647</v>
       </c>
       <c r="I63">
-        <v>114.0</v>
+        <v>154.0</v>
       </c>
       <c r="J63">
-        <v>40.9817849126308</v>
+        <v>34.95170513266686</v>
       </c>
       <c r="K63">
-        <v>0.15491194628143726</v>
+        <v>0.03870119174792897</v>
       </c>
       <c r="L63">
-        <v>0.5228481346079389</v>
+        <v>0.17319011601370443</v>
       </c>
       <c r="M63">
-        <v>0.6349717785734288</v>
+        <v>0.15837892637061693</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Exact</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="O63">
-        <v>20.0</v>
+        <v>50.0</v>
       </c>
       <c r="P63">
-        <v>3.098238925628745</v>
+        <v>1.9350595873964487</v>
       </c>
       <c r="Q63">
-        <v>44.08002383825954</v>
+        <v>36.88676472006331</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E64">
@@ -4283,66 +4283,66 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="H64">
-        <v>0.3594893413388667</v>
+        <v>0.22695912423809647</v>
       </c>
       <c r="I64">
-        <v>114.0</v>
+        <v>154.0</v>
       </c>
       <c r="J64">
-        <v>40.9817849126308</v>
+        <v>34.95170513266686</v>
       </c>
       <c r="K64">
-        <v>0.02224456946486678</v>
+        <v>0.017807566680299383</v>
       </c>
       <c r="L64">
-        <v>0.07507833920524419</v>
+        <v>0.07968991134356651</v>
       </c>
       <c r="M64">
-        <v>0.0701374812037044</v>
+        <v>0.04048602416961191</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Mega rare</t>
         </is>
       </c>
       <c r="O64">
-        <v>50.0</v>
+        <v>70.0</v>
       </c>
       <c r="P64">
-        <v>1.112228473243339</v>
+        <v>1.2465296676209567</v>
       </c>
       <c r="Q64">
-        <v>42.09401338587414</v>
+        <v>36.198234800287814</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E65">
@@ -4350,66 +4350,66 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>3-3</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H65">
-        <v>0.3594893413388667</v>
+        <v>0.22695912423809647</v>
       </c>
       <c r="I65">
-        <v>114.0</v>
+        <v>154.0</v>
       </c>
       <c r="J65">
-        <v>40.9817849126308</v>
+        <v>34.95170513266686</v>
       </c>
       <c r="K65">
-        <v>0.004513367907492568</v>
+        <v>0.05581174878769681</v>
       </c>
       <c r="L65">
-        <v>0.015233208592864964</v>
+        <v>0.24976086810004244</v>
       </c>
       <c r="M65">
-        <v>0.00569228830932662</v>
+        <v>0.38066893432444177</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Mega rare</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="O65">
-        <v>70.0</v>
+        <v>20.0</v>
       </c>
       <c r="P65">
-        <v>0.3159357535244798</v>
+        <v>1.1162349757539363</v>
       </c>
       <c r="Q65">
-        <v>41.29772066615528</v>
+        <v>36.06794010842079</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E66">
@@ -4417,66 +4417,66 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H66">
-        <v>0.3594893413388667</v>
+        <v>0.22695912423809647</v>
       </c>
       <c r="I66">
-        <v>114.0</v>
+        <v>154.0</v>
       </c>
       <c r="J66">
-        <v>40.9817849126308</v>
+        <v>34.95170513266686</v>
       </c>
       <c r="K66">
-        <v>0.0001384932281133703</v>
+        <v>0.012782872380586553</v>
       </c>
       <c r="L66">
-        <v>0.0004674328075599438</v>
+        <v>0.05720410795103318</v>
       </c>
       <c r="M66">
-        <v>0.00043667135023599924</v>
+        <v>0.061030692617485734</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Ultra rare</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="O66">
-        <v>100.0</v>
+        <v>50.0</v>
       </c>
       <c r="P66">
-        <v>0.01384932281133703</v>
+        <v>0.6391436190293276</v>
       </c>
       <c r="Q66">
-        <v>40.99563423544214</v>
+        <v>35.590848751696186</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="E67">
@@ -4484,31 +4484,31 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H67">
-        <v>0.8254677498017804</v>
+        <v>0.5490221463968763</v>
       </c>
       <c r="I67">
-        <v>32.0</v>
+        <v>63.0</v>
       </c>
       <c r="J67">
-        <v>26.414967993656973</v>
+        <v>34.588395223003204</v>
       </c>
       <c r="K67">
-        <v>0.1748048413099816</v>
+        <v>0.11959153082740943</v>
       </c>
       <c r="L67">
-        <v>0.2071837937146534</v>
+        <v>0.22338200542014444</v>
       </c>
       <c r="M67">
-        <v>0.18749979658595534</v>
+        <v>0.18473383869234788</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
@@ -4519,31 +4519,31 @@
         <v>50.0</v>
       </c>
       <c r="P67">
-        <v>8.74024206549908</v>
+        <v>5.979576541370472</v>
       </c>
       <c r="Q67">
-        <v>35.155210059156055</v>
+        <v>40.567971764373674</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="E68">
@@ -4551,31 +4551,31 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H68">
-        <v>0.8254677498017804</v>
+        <v>0.5490221463968763</v>
       </c>
       <c r="I68">
-        <v>32.0</v>
+        <v>63.0</v>
       </c>
       <c r="J68">
-        <v>26.414967993656973</v>
+        <v>34.588395223003204</v>
       </c>
       <c r="K68">
-        <v>0.10928616146098369</v>
+        <v>0.10910156576700879</v>
       </c>
       <c r="L68">
-        <v>0.1295291444007955</v>
+        <v>0.2037880641454795</v>
       </c>
       <c r="M68">
-        <v>0.14327245159063542</v>
+        <v>0.18959615932706256</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
@@ -4586,31 +4586,31 @@
         <v>50.0</v>
       </c>
       <c r="P68">
-        <v>5.464308073049184</v>
+        <v>5.455078288350439</v>
       </c>
       <c r="Q68">
-        <v>31.879276066706158</v>
+        <v>40.04347351135364</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="E69">
@@ -4618,66 +4618,66 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H69">
-        <v>0.8254677498017804</v>
+        <v>0.5490221463968763</v>
       </c>
       <c r="I69">
-        <v>32.0</v>
+        <v>63.0</v>
       </c>
       <c r="J69">
-        <v>26.414967993656973</v>
+        <v>34.588395223003204</v>
       </c>
       <c r="K69">
-        <v>0.09892727319626002</v>
+        <v>0.0978372970163203</v>
       </c>
       <c r="L69">
-        <v>0.11725148805404818</v>
+        <v>0.18274782052863336</v>
       </c>
       <c r="M69">
-        <v>0.17685287834991267</v>
+        <v>0.28336861502746963</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="O69">
-        <v>50.0</v>
+        <v>30.0</v>
       </c>
       <c r="P69">
-        <v>4.9463636598130005</v>
+        <v>2.9351189104896087</v>
       </c>
       <c r="Q69">
-        <v>31.361331653469975</v>
+        <v>37.52351413349281</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="E70">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4694,22 +4694,22 @@
         </is>
       </c>
       <c r="H70">
-        <v>0.8254677498017804</v>
+        <v>0.21871790150957568</v>
       </c>
       <c r="I70">
-        <v>32.0</v>
+        <v>158.0</v>
       </c>
       <c r="J70">
-        <v>26.414967993656973</v>
+        <v>34.55742843851296</v>
       </c>
       <c r="K70">
-        <v>0.07991036952440392</v>
+        <v>0.05866311715411285</v>
       </c>
       <c r="L70">
-        <v>0.09471209945408102</v>
+        <v>0.24217415570076148</v>
       </c>
       <c r="M70">
-        <v>0.07618999778343705</v>
+        <v>0.18927087388158162</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
@@ -4720,31 +4720,31 @@
         <v>50.0</v>
       </c>
       <c r="P70">
-        <v>3.995518476220196</v>
+        <v>2.9331558577056422</v>
       </c>
       <c r="Q70">
-        <v>30.410486469877167</v>
+        <v>37.4905842962186</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="E71">
@@ -4752,66 +4752,66 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="H71">
-        <v>0.8254677498017804</v>
+        <v>0.5490221463968763</v>
       </c>
       <c r="I71">
-        <v>32.0</v>
+        <v>63.0</v>
       </c>
       <c r="J71">
-        <v>26.414967993656973</v>
+        <v>34.588395223003204</v>
       </c>
       <c r="K71">
-        <v>0.06878623558200987</v>
+        <v>0.03457892957996819</v>
       </c>
       <c r="L71">
-        <v>0.08152745162222752</v>
+        <v>0.06458911079583653</v>
       </c>
       <c r="M71">
-        <v>0.08607869551382188</v>
+        <v>0.03338394008225541</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Mega rare</t>
         </is>
       </c>
       <c r="O71">
-        <v>50.0</v>
+        <v>70.0</v>
       </c>
       <c r="P71">
-        <v>3.4393117791004935</v>
+        <v>2.4205250705977734</v>
       </c>
       <c r="Q71">
-        <v>29.854279772757465</v>
+        <v>37.00892029360098</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="E72">
@@ -4824,61 +4824,61 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="H72">
-        <v>0.2907922410598463</v>
+        <v>0.41817785250366857</v>
       </c>
       <c r="I72">
-        <v>120.0</v>
+        <v>103.0</v>
       </c>
       <c r="J72">
-        <v>34.895068927181555</v>
+        <v>43.07231880787786</v>
       </c>
       <c r="K72">
-        <v>0.1086618114141417</v>
+        <v>0.11352058001715237</v>
       </c>
       <c r="L72">
-        <v>0.44098819048220544</v>
+        <v>0.3702626139624578</v>
       </c>
       <c r="M72">
-        <v>0.5561365994498195</v>
+        <v>0.2731696742292041</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Exact</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="O72">
-        <v>20.0</v>
+        <v>30.0</v>
       </c>
       <c r="P72">
-        <v>2.173236228282834</v>
+        <v>3.405617400514571</v>
       </c>
       <c r="Q72">
-        <v>37.06830515546439</v>
+        <v>46.477936208392435</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="E73">
@@ -4891,26 +4891,26 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="H73">
-        <v>0.2907922410598463</v>
+        <v>0.41817785250366857</v>
       </c>
       <c r="I73">
-        <v>120.0</v>
+        <v>103.0</v>
       </c>
       <c r="J73">
-        <v>34.895068927181555</v>
+        <v>43.07231880787786</v>
       </c>
       <c r="K73">
-        <v>0.1042289116354038</v>
+        <v>0.1692546202773764</v>
       </c>
       <c r="L73">
-        <v>0.4229979101199164</v>
+        <v>0.5520466695964352</v>
       </c>
       <c r="M73">
-        <v>0.32827618221736715</v>
+        <v>0.6618381257253579</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
@@ -4921,31 +4921,31 @@
         <v>20.0</v>
       </c>
       <c r="P73">
-        <v>2.084578232708076</v>
+        <v>3.3850924055475278</v>
       </c>
       <c r="Q73">
-        <v>36.97964715988963</v>
+        <v>46.45741121342539</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="E74">
@@ -4962,22 +4962,22 @@
         </is>
       </c>
       <c r="H74">
-        <v>0.2907922410598463</v>
+        <v>0.41817785250366857</v>
       </c>
       <c r="I74">
-        <v>120.0</v>
+        <v>103.0</v>
       </c>
       <c r="J74">
-        <v>34.895068927181555</v>
+        <v>43.07231880787786</v>
       </c>
       <c r="K74">
-        <v>0.02629281040414408</v>
+        <v>0.020023786895253384</v>
       </c>
       <c r="L74">
-        <v>0.1067055548947549</v>
+        <v>0.06531026952243812</v>
       </c>
       <c r="M74">
-        <v>0.10351378619195022</v>
+        <v>0.06023017304643022</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
@@ -4988,31 +4988,31 @@
         <v>50.0</v>
       </c>
       <c r="P74">
-        <v>1.314640520207204</v>
+        <v>1.0011893447626692</v>
       </c>
       <c r="Q74">
-        <v>36.20970944738876</v>
+        <v>44.073508152640535</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="E75">
@@ -5029,57 +5029,57 @@
         </is>
       </c>
       <c r="H75">
-        <v>0.2907922410598463</v>
+        <v>0.41817785250366857</v>
       </c>
       <c r="I75">
-        <v>120.0</v>
+        <v>103.0</v>
       </c>
       <c r="J75">
-        <v>34.895068927181555</v>
+        <v>43.07231880787786</v>
       </c>
       <c r="K75">
-        <v>0.006925070980960388</v>
+        <v>0.0036877055792596944</v>
       </c>
       <c r="L75">
-        <v>0.028104395473542685</v>
+        <v>0.012027946889403897</v>
       </c>
       <c r="M75">
-        <v>0.010905495546025457</v>
+        <v>0.004436945845358528</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Mega rare</t>
+          <t>Ultra rare</t>
         </is>
       </c>
       <c r="O75">
-        <v>70.0</v>
+        <v>100.0</v>
       </c>
       <c r="P75">
-        <v>0.4847549686672271</v>
+        <v>0.3687705579259694</v>
       </c>
       <c r="Q75">
-        <v>35.37982389584878</v>
+        <v>43.44108936580383</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="E76">
@@ -5087,66 +5087,66 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>4-4</t>
         </is>
       </c>
       <c r="H76">
-        <v>0.5370178824283498</v>
+        <v>0.41817785250366857</v>
       </c>
       <c r="I76">
-        <v>57.0</v>
+        <v>103.0</v>
       </c>
       <c r="J76">
-        <v>30.61001929841594</v>
+        <v>43.07231880787786</v>
       </c>
       <c r="K76">
-        <v>0.15395749666507266</v>
+        <v>0.00010271108948726918</v>
       </c>
       <c r="L76">
-        <v>0.2866034083789173</v>
+        <v>0.0003350060092253058</v>
       </c>
       <c r="M76">
-        <v>0.2366969142640503</v>
+        <v>0.00030894788912640993</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Ultra rare</t>
         </is>
       </c>
       <c r="O76">
-        <v>30.0</v>
+        <v>100.0</v>
       </c>
       <c r="P76">
-        <v>4.61872489995218</v>
+        <v>0.01027110894872692</v>
       </c>
       <c r="Q76">
-        <v>35.22874419836812</v>
+        <v>43.08258991682659</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E77">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5163,57 +5163,57 @@
         </is>
       </c>
       <c r="H77">
-        <v>0.8184599716980068</v>
+        <v>0.8094261393873677</v>
       </c>
       <c r="I77">
         <v>32.0</v>
       </c>
       <c r="J77">
-        <v>26.190719094336217</v>
+        <v>25.901636460395768</v>
       </c>
       <c r="K77">
-        <v>0.16843732611723336</v>
+        <v>0.19302628434009309</v>
       </c>
       <c r="L77">
-        <v>0.20080409803316937</v>
+        <v>0.23534744528688345</v>
       </c>
       <c r="M77">
-        <v>0.18204236744273028</v>
+        <v>0.21235826374942837</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="O77">
-        <v>50.0</v>
+        <v>30.0</v>
       </c>
       <c r="P77">
-        <v>8.421866305861668</v>
+        <v>5.790788530202793</v>
       </c>
       <c r="Q77">
-        <v>34.61258540019789</v>
+        <v>31.69242499059856</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E78">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5230,22 +5230,22 @@
         </is>
       </c>
       <c r="H78">
-        <v>0.8184599716980068</v>
+        <v>0.8094261393873677</v>
       </c>
       <c r="I78">
         <v>32.0</v>
       </c>
       <c r="J78">
-        <v>26.190719094336217</v>
+        <v>25.901636460395768</v>
       </c>
       <c r="K78">
-        <v>0.10562410866354016</v>
+        <v>0.1096743924732736</v>
       </c>
       <c r="L78">
-        <v>0.12592074666382166</v>
+        <v>0.13372058717401664</v>
       </c>
       <c r="M78">
-        <v>0.13952350222098386</v>
+        <v>0.14747151034852446</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
@@ -5256,31 +5256,31 @@
         <v>50.0</v>
       </c>
       <c r="P78">
-        <v>5.281205433177008</v>
+        <v>5.48371962366368</v>
       </c>
       <c r="Q78">
-        <v>31.471924527513224</v>
+        <v>31.385356084059445</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E79">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5297,22 +5297,22 @@
         </is>
       </c>
       <c r="H79">
-        <v>0.8184599716980068</v>
+        <v>0.8094261393873677</v>
       </c>
       <c r="I79">
         <v>32.0</v>
       </c>
       <c r="J79">
-        <v>26.190719094336217</v>
+        <v>25.901636460395768</v>
       </c>
       <c r="K79">
-        <v>0.10084624052317352</v>
+        <v>0.10249440282640576</v>
       </c>
       <c r="L79">
-        <v>0.12022476748531118</v>
+        <v>0.12496637928800992</v>
       </c>
       <c r="M79">
-        <v>0.18165301001196565</v>
+        <v>0.18793238014761185</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
@@ -5323,31 +5323,31 @@
         <v>50.0</v>
       </c>
       <c r="P79">
-        <v>5.042312026158676</v>
+        <v>5.124720141320288</v>
       </c>
       <c r="Q79">
-        <v>31.233031120494893</v>
+        <v>31.026356601716056</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E80">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5364,22 +5364,22 @@
         </is>
       </c>
       <c r="H80">
-        <v>0.8184599716980068</v>
+        <v>0.8094261393873677</v>
       </c>
       <c r="I80">
         <v>32.0</v>
       </c>
       <c r="J80">
-        <v>26.190719094336217</v>
+        <v>25.901636460395768</v>
       </c>
       <c r="K80">
-        <v>0.07676707939567261</v>
+        <v>0.0970932553580134</v>
       </c>
       <c r="L80">
-        <v>0.09151857543713149</v>
+        <v>0.11838102609297961</v>
       </c>
       <c r="M80">
-        <v>0.07374908425451017</v>
+        <v>0.09494875074816131</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
@@ -5390,31 +5390,31 @@
         <v>50.0</v>
       </c>
       <c r="P80">
-        <v>3.8383539697836304</v>
+        <v>4.85466276790067</v>
       </c>
       <c r="Q80">
-        <v>30.029073064119846</v>
+        <v>30.756299228296438</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E81">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5431,22 +5431,22 @@
         </is>
       </c>
       <c r="H81">
-        <v>0.8184599716980068</v>
+        <v>0.8094261393873677</v>
       </c>
       <c r="I81">
         <v>32.0</v>
       </c>
       <c r="J81">
-        <v>26.190719094336217</v>
+        <v>25.901636460395768</v>
       </c>
       <c r="K81">
-        <v>0.07033285059802338</v>
+        <v>0.06476833377237173</v>
       </c>
       <c r="L81">
-        <v>0.08384795076008252</v>
+        <v>0.07896884064741724</v>
       </c>
       <c r="M81">
-        <v>0.0886827487400672</v>
+        <v>0.08313085155739457</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
@@ -5457,1353 +5457,13 @@
         <v>50.0</v>
       </c>
       <c r="P81">
-        <v>3.516642529901169</v>
+        <v>3.2384166886185866</v>
       </c>
       <c r="Q81">
-        <v>29.707361624237386</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>01:30</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E82">
-        <v>1</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="H82">
-        <v>0.2301762567942824</v>
-      </c>
-      <c r="I82">
-        <v>154.0</v>
-      </c>
-      <c r="J82">
-        <v>35.447143546319495</v>
-      </c>
-      <c r="K82">
-        <v>0.07546185915738286</v>
-      </c>
-      <c r="L82">
-        <v>0.3294693036444912</v>
-      </c>
-      <c r="M82">
-        <v>0.26789946104973894</v>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="O82">
-        <v>30.0</v>
-      </c>
-      <c r="P82">
-        <v>2.263855774721486</v>
-      </c>
-      <c r="Q82">
-        <v>37.71099932104098</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>01:30</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E83">
-        <v>2</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="H83">
-        <v>0.2301762567942824</v>
-      </c>
-      <c r="I83">
-        <v>154.0</v>
-      </c>
-      <c r="J83">
-        <v>35.447143546319495</v>
-      </c>
-      <c r="K83">
-        <v>0.03963664561168222</v>
-      </c>
-      <c r="L83">
-        <v>0.17305507940439838</v>
-      </c>
-      <c r="M83">
-        <v>0.1583046804071361</v>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>Tres rare</t>
-        </is>
-      </c>
-      <c r="O83">
-        <v>50.0</v>
-      </c>
-      <c r="P83">
-        <v>1.9818322805841109</v>
-      </c>
-      <c r="Q83">
-        <v>37.4289758269036</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>01:30</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E84">
-        <v>3</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>3-2</t>
-        </is>
-      </c>
-      <c r="H84">
-        <v>0.2301762567942824</v>
-      </c>
-      <c r="I84">
-        <v>154.0</v>
-      </c>
-      <c r="J84">
-        <v>35.447143546319495</v>
-      </c>
-      <c r="K84">
-        <v>0.0187670706783498</v>
-      </c>
-      <c r="L84">
-        <v>0.0819377335369814</v>
-      </c>
-      <c r="M84">
-        <v>0.041640970819166984</v>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>Mega rare</t>
-        </is>
-      </c>
-      <c r="O84">
-        <v>70.0</v>
-      </c>
-      <c r="P84">
-        <v>1.3136949474844861</v>
-      </c>
-      <c r="Q84">
-        <v>36.76083849380398</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>01:30</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E85">
-        <v>4</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="H85">
-        <v>0.2301762567942824</v>
-      </c>
-      <c r="I85">
-        <v>154.0</v>
-      </c>
-      <c r="J85">
-        <v>35.447143546319495</v>
-      </c>
-      <c r="K85">
-        <v>0.05725460935022574</v>
-      </c>
-      <c r="L85">
-        <v>0.24997576900026205</v>
-      </c>
-      <c r="M85">
-        <v>0.38111502185036694</v>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="O85">
-        <v>20.0</v>
-      </c>
-      <c r="P85">
-        <v>1.1450921870045148</v>
-      </c>
-      <c r="Q85">
-        <v>36.59223573332401</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>01:30</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E86">
-        <v>5</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
-      <c r="H86">
-        <v>0.2301762567942824</v>
-      </c>
-      <c r="I86">
-        <v>154.0</v>
-      </c>
-      <c r="J86">
-        <v>35.447143546319495</v>
-      </c>
-      <c r="K86">
-        <v>0.013449560517746857</v>
-      </c>
-      <c r="L86">
-        <v>0.058721284998621295</v>
-      </c>
-      <c r="M86">
-        <v>0.06266885279875029</v>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>Tres rare</t>
-        </is>
-      </c>
-      <c r="O86">
-        <v>50.0</v>
-      </c>
-      <c r="P86">
-        <v>0.6724780258873428</v>
-      </c>
-      <c r="Q86">
-        <v>36.11962157220684</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>01:30</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="E87">
-        <v>1</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="H87">
-        <v>0.5455277196050351</v>
-      </c>
-      <c r="I87">
-        <v>63.0</v>
-      </c>
-      <c r="J87">
-        <v>34.36824633511721</v>
-      </c>
-      <c r="K87">
-        <v>0.11906730647452264</v>
-      </c>
-      <c r="L87">
-        <v>0.2235380300118988</v>
-      </c>
-      <c r="M87">
-        <v>0.18485668462140056</v>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>Tres rare</t>
-        </is>
-      </c>
-      <c r="O87">
-        <v>50.0</v>
-      </c>
-      <c r="P87">
-        <v>5.953365323726132</v>
-      </c>
-      <c r="Q87">
-        <v>40.321611658843345</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>01:30</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="E88">
-        <v>2</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="H88">
-        <v>0.5455277196050351</v>
-      </c>
-      <c r="I88">
-        <v>63.0</v>
-      </c>
-      <c r="J88">
-        <v>34.36824633511721</v>
-      </c>
-      <c r="K88">
-        <v>0.10830765310352058</v>
-      </c>
-      <c r="L88">
-        <v>0.20333776018653463</v>
-      </c>
-      <c r="M88">
-        <v>0.18917088617975356</v>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>Tres rare</t>
-        </is>
-      </c>
-      <c r="O88">
-        <v>50.0</v>
-      </c>
-      <c r="P88">
-        <v>5.415382655176029</v>
-      </c>
-      <c r="Q88">
-        <v>39.783628990293245</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>01:30</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="E89">
-        <v>3</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="H89">
-        <v>0.22027792442874564</v>
-      </c>
-      <c r="I89">
-        <v>158.0</v>
-      </c>
-      <c r="J89">
-        <v>34.80391205974181</v>
-      </c>
-      <c r="K89">
-        <v>0.05894066364734484</v>
-      </c>
-      <c r="L89">
-        <v>0.2409727154143593</v>
-      </c>
-      <c r="M89">
-        <v>0.1883777945257469</v>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>Tres rare</t>
-        </is>
-      </c>
-      <c r="O89">
-        <v>50.0</v>
-      </c>
-      <c r="P89">
-        <v>2.947033182367242</v>
-      </c>
-      <c r="Q89">
-        <v>37.750945242109054</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>01:30</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="E90">
-        <v>4</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="H90">
-        <v>0.5455277196050351</v>
-      </c>
-      <c r="I90">
-        <v>63.0</v>
-      </c>
-      <c r="J90">
-        <v>34.36824633511721</v>
-      </c>
-      <c r="K90">
-        <v>0.09772967325768614</v>
-      </c>
-      <c r="L90">
-        <v>0.18347856586815672</v>
-      </c>
-      <c r="M90">
-        <v>0.28449219063254577</v>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="O90">
-        <v>30.0</v>
-      </c>
-      <c r="P90">
-        <v>2.931890197730584</v>
-      </c>
-      <c r="Q90">
-        <v>37.300136532847795</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>01:30</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="E91">
-        <v>5</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="H91">
-        <v>0.22027792442874564</v>
-      </c>
-      <c r="I91">
-        <v>158.0</v>
-      </c>
-      <c r="J91">
-        <v>34.80391205974181</v>
-      </c>
-      <c r="K91">
-        <v>0.04524044043483679</v>
-      </c>
-      <c r="L91">
-        <v>0.1849607911331229</v>
-      </c>
-      <c r="M91">
-        <v>0.16266496843187267</v>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>Tres rare</t>
-        </is>
-      </c>
-      <c r="O91">
-        <v>50.0</v>
-      </c>
-      <c r="P91">
-        <v>2.2620220217418394</v>
-      </c>
-      <c r="Q91">
-        <v>37.065934081483654</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="E92">
-        <v>1</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Draw</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="H92">
-        <v>0.4156205913878908</v>
-      </c>
-      <c r="I92">
-        <v>103.0</v>
-      </c>
-      <c r="J92">
-        <v>42.80892091295275</v>
-      </c>
-      <c r="K92">
-        <v>0.11354947439044177</v>
-      </c>
-      <c r="L92">
-        <v>0.3718702897027684</v>
-      </c>
-      <c r="M92">
-        <v>0.2746934344257886</v>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="O92">
-        <v>30.0</v>
-      </c>
-      <c r="P92">
-        <v>3.4064842317132533</v>
-      </c>
-      <c r="Q92">
-        <v>46.215405144666</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="E93">
-        <v>2</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Draw</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
-      <c r="H93">
-        <v>0.4156205913878908</v>
-      </c>
-      <c r="I93">
-        <v>103.0</v>
-      </c>
-      <c r="J93">
-        <v>42.80892091295275</v>
-      </c>
-      <c r="K93">
-        <v>0.16770874087689283</v>
-      </c>
-      <c r="L93">
-        <v>0.5492398656213103</v>
-      </c>
-      <c r="M93">
-        <v>0.6592835121056831</v>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="O93">
-        <v>20.0</v>
-      </c>
-      <c r="P93">
-        <v>3.3541748175378565</v>
-      </c>
-      <c r="Q93">
-        <v>46.16309573049061</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="E94">
-        <v>3</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Draw</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>2-2</t>
-        </is>
-      </c>
-      <c r="H94">
-        <v>0.4156205913878908</v>
-      </c>
-      <c r="I94">
-        <v>103.0</v>
-      </c>
-      <c r="J94">
-        <v>42.80892091295275</v>
-      </c>
-      <c r="K94">
-        <v>0.020218647595547222</v>
-      </c>
-      <c r="L94">
-        <v>0.06621531609121414</v>
-      </c>
-      <c r="M94">
-        <v>0.06113997639883714</v>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>Tres rare</t>
-        </is>
-      </c>
-      <c r="O94">
-        <v>50.0</v>
-      </c>
-      <c r="P94">
-        <v>1.010932379777361</v>
-      </c>
-      <c r="Q94">
-        <v>43.81985329273011</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="E95">
-        <v>4</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Draw</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>3-3</t>
-        </is>
-      </c>
-      <c r="H95">
-        <v>0.4156205913878908</v>
-      </c>
-      <c r="I95">
-        <v>103.0</v>
-      </c>
-      <c r="J95">
-        <v>42.80892091295275</v>
-      </c>
-      <c r="K95">
-        <v>0.0037588715906637492</v>
-      </c>
-      <c r="L95">
-        <v>0.012310164136640845</v>
-      </c>
-      <c r="M95">
-        <v>0.004546640802821135</v>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>Ultra rare</t>
-        </is>
-      </c>
-      <c r="O95">
-        <v>100.0</v>
-      </c>
-      <c r="P95">
-        <v>0.37588715906637493</v>
-      </c>
-      <c r="Q95">
-        <v>43.18480807201912</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="E96">
-        <v>5</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Draw</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>4-4</t>
-        </is>
-      </c>
-      <c r="H96">
-        <v>0.4156205913878908</v>
-      </c>
-      <c r="I96">
-        <v>103.0</v>
-      </c>
-      <c r="J96">
-        <v>42.80892091295275</v>
-      </c>
-      <c r="K96">
-        <v>0.00010568514475574372</v>
-      </c>
-      <c r="L96">
-        <v>0.0003461149037331491</v>
-      </c>
-      <c r="M96">
-        <v>0.0003195855323922309</v>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>Ultra rare</t>
-        </is>
-      </c>
-      <c r="O96">
-        <v>100.0</v>
-      </c>
-      <c r="P96">
-        <v>0.010568514475574371</v>
-      </c>
-      <c r="Q96">
-        <v>42.81948942742832</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="E97">
-        <v>1</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="H97">
-        <v>0.8060386414102592</v>
-      </c>
-      <c r="I97">
-        <v>32.0</v>
-      </c>
-      <c r="J97">
-        <v>25.793236525128293</v>
-      </c>
-      <c r="K97">
-        <v>0.19348857453700932</v>
-      </c>
-      <c r="L97">
-        <v>0.23745655995783146</v>
-      </c>
-      <c r="M97">
-        <v>0.21424908463602002</v>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="O97">
-        <v>30.0</v>
-      </c>
-      <c r="P97">
-        <v>5.8046572361102795</v>
-      </c>
-      <c r="Q97">
-        <v>31.597893761238574</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="E98">
-        <v>2</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>0-3</t>
-        </is>
-      </c>
-      <c r="H98">
-        <v>0.8060386414102592</v>
-      </c>
-      <c r="I98">
-        <v>32.0</v>
-      </c>
-      <c r="J98">
-        <v>25.793236525128293</v>
-      </c>
-      <c r="K98">
-        <v>0.10843039066453089</v>
-      </c>
-      <c r="L98">
-        <v>0.13306991187305708</v>
-      </c>
-      <c r="M98">
-        <v>0.14674551888146714</v>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>Tres rare</t>
-        </is>
-      </c>
-      <c r="O98">
-        <v>50.0</v>
-      </c>
-      <c r="P98">
-        <v>5.421519533226545</v>
-      </c>
-      <c r="Q98">
-        <v>31.214756058354837</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="E99">
-        <v>3</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="H99">
-        <v>0.8060386414102592</v>
-      </c>
-      <c r="I99">
-        <v>32.0</v>
-      </c>
-      <c r="J99">
-        <v>25.793236525128293</v>
-      </c>
-      <c r="K99">
-        <v>0.10358943171536036</v>
-      </c>
-      <c r="L99">
-        <v>0.1271289023756346</v>
-      </c>
-      <c r="M99">
-        <v>0.19117356994754864</v>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>Tres rare</t>
-        </is>
-      </c>
-      <c r="O99">
-        <v>50.0</v>
-      </c>
-      <c r="P99">
-        <v>5.1794715857680185</v>
-      </c>
-      <c r="Q99">
-        <v>30.972708110896313</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="E100">
-        <v>4</v>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="H100">
-        <v>0.8060386414102592</v>
-      </c>
-      <c r="I100">
-        <v>32.0</v>
-      </c>
-      <c r="J100">
-        <v>25.793236525128293</v>
-      </c>
-      <c r="K100">
-        <v>0.09867815615296358</v>
-      </c>
-      <c r="L100">
-        <v>0.12110159764799219</v>
-      </c>
-      <c r="M100">
-        <v>0.09712525084316524</v>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>Tres rare</t>
-        </is>
-      </c>
-      <c r="O100">
-        <v>50.0</v>
-      </c>
-      <c r="P100">
-        <v>4.933907807648179</v>
-      </c>
-      <c r="Q100">
-        <v>30.727144332776472</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="E101">
-        <v>5</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>1-3</t>
-        </is>
-      </c>
-      <c r="H101">
-        <v>0.8060386414102592</v>
-      </c>
-      <c r="I101">
-        <v>32.0</v>
-      </c>
-      <c r="J101">
-        <v>25.793236525128293</v>
-      </c>
-      <c r="K101">
-        <v>0.06456318349674803</v>
-      </c>
-      <c r="L101">
-        <v>0.07923440177151965</v>
-      </c>
-      <c r="M101">
-        <v>0.08340563173584091</v>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>Tres rare</t>
-        </is>
-      </c>
-      <c r="O101">
-        <v>50.0</v>
-      </c>
-      <c r="P101">
-        <v>3.2281591748374012</v>
-      </c>
-      <c r="Q101">
-        <v>29.021395699965694</v>
+        <v>29.140053149014353</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q101"/>
+  <autoFilter ref="A1:Q81"/>
 </worksheet>
 </file>
--- a/data/mpg/mpg_round3_top5_bets.xlsx
+++ b/data/mpg/mpg_round3_top5_bets.xlsx
@@ -129,45 +129,45 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H2">
-        <v>0.4033014374680687</v>
+        <v>0.5092867836944935</v>
       </c>
       <c r="I2">
-        <v>108.0</v>
+        <v>96.0</v>
       </c>
       <c r="J2">
-        <v>43.55655524655142</v>
+        <v>48.891531234671376</v>
       </c>
       <c r="K2">
-        <v>0.3034148547376874</v>
+        <v>0.11055701804772465</v>
       </c>
       <c r="L2">
-        <v>0.7508755811175876</v>
+        <v>0.21694311728211282</v>
       </c>
       <c r="M2">
-        <v>0.8282858904878876</v>
+        <v>0.17955358356768283</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Exact</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="O2">
-        <v>20.0</v>
+        <v>50.0</v>
       </c>
       <c r="P2">
-        <v>6.068297094753748</v>
+        <v>5.527850902386232</v>
       </c>
       <c r="Q2">
-        <v>49.624852341305164</v>
+        <v>54.41938213705761</v>
       </c>
     </row>
     <row r="3">
@@ -196,31 +196,31 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H3">
-        <v>0.4033014374680687</v>
+        <v>0.5092867836944935</v>
       </c>
       <c r="I3">
-        <v>108.0</v>
+        <v>96.0</v>
       </c>
       <c r="J3">
-        <v>43.55655524655142</v>
+        <v>48.891531234671376</v>
       </c>
       <c r="K3">
-        <v>0.09260282764414957</v>
+        <v>0.09963162213064454</v>
       </c>
       <c r="L3">
-        <v>0.2291687467989873</v>
+        <v>0.1955045013566229</v>
       </c>
       <c r="M3">
-        <v>0.15556586453121213</v>
+        <v>0.18203608413450684</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -231,10 +231,10 @@
         <v>50.0</v>
       </c>
       <c r="P3">
-        <v>4.630141382207478</v>
+        <v>4.981581106532227</v>
       </c>
       <c r="Q3">
-        <v>48.186696628758895</v>
+        <v>53.8731123412036</v>
       </c>
     </row>
     <row r="4">
@@ -263,45 +263,45 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H4">
-        <v>0.4033014374680687</v>
+        <v>0.5092867836944935</v>
       </c>
       <c r="I4">
-        <v>108.0</v>
+        <v>96.0</v>
       </c>
       <c r="J4">
-        <v>43.55655524655142</v>
+        <v>48.891531234671376</v>
       </c>
       <c r="K4">
-        <v>0.007432744453083944</v>
+        <v>0.09695442895789146</v>
       </c>
       <c r="L4">
-        <v>0.01839417623548114</v>
+        <v>0.19025111588440685</v>
       </c>
       <c r="M4">
-        <v>0.0156080724814215</v>
+        <v>0.29524101233389566</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Mega rare</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="O4">
-        <v>70.0</v>
+        <v>30.0</v>
       </c>
       <c r="P4">
-        <v>0.5202921117158761</v>
+        <v>2.9086328687367438</v>
       </c>
       <c r="Q4">
-        <v>44.076847358267294</v>
+        <v>51.80016410340812</v>
       </c>
     </row>
     <row r="5">
@@ -330,45 +330,45 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3-3</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="H5">
-        <v>0.4033014374680687</v>
+        <v>0.5092867836944935</v>
       </c>
       <c r="I5">
-        <v>108.0</v>
+        <v>96.0</v>
       </c>
       <c r="J5">
-        <v>43.55655524655142</v>
+        <v>48.891531234671376</v>
       </c>
       <c r="K5">
-        <v>0.0006228917335824087</v>
+        <v>0.03673263369164942</v>
       </c>
       <c r="L5">
-        <v>0.0015415006388905632</v>
+        <v>0.07207947717627859</v>
       </c>
       <c r="M5">
-        <v>0.0005232058972133063</v>
+        <v>0.03728548925297283</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Ultra rare</t>
+          <t>Mega rare</t>
         </is>
       </c>
       <c r="O5">
-        <v>100.0</v>
+        <v>70.0</v>
       </c>
       <c r="P5">
-        <v>0.062289173358240864</v>
+        <v>2.5712843584154594</v>
       </c>
       <c r="Q5">
-        <v>43.61884441990966</v>
+        <v>51.46281559308684</v>
       </c>
     </row>
     <row r="6">
@@ -397,45 +397,45 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="H6">
-        <v>0.4033014374680687</v>
+        <v>0.5092867836944935</v>
       </c>
       <c r="I6">
-        <v>108.0</v>
+        <v>96.0</v>
       </c>
       <c r="J6">
-        <v>43.55655524655142</v>
+        <v>48.891531234671376</v>
       </c>
       <c r="K6">
-        <v>7.894543154473964e-06</v>
+        <v>0.031889547849941094</v>
       </c>
       <c r="L6">
-        <v>1.9537012068503745e-05</v>
+        <v>0.0625760177096754</v>
       </c>
       <c r="M6">
-        <v>1.6577806830371323e-05</v>
+        <v>0.03236951108984722</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Ultra rare</t>
+          <t>Mega rare</t>
         </is>
       </c>
       <c r="O6">
-        <v>100.0</v>
+        <v>70.0</v>
       </c>
       <c r="P6">
-        <v>0.0007894543154473964</v>
+        <v>2.2322683494958766</v>
       </c>
       <c r="Q6">
-        <v>43.557344700866864</v>
+        <v>51.12379958416725</v>
       </c>
     </row>
     <row r="7">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="H7">
-        <v>0.967577190262213</v>
+        <v>0.8686669773038992</v>
       </c>
       <c r="I7">
         <v>56.0</v>
       </c>
       <c r="J7">
-        <v>54.184322654683925</v>
+        <v>48.645350729018354</v>
       </c>
       <c r="K7">
-        <v>0.16682026612393575</v>
+        <v>0.17800937997727778</v>
       </c>
       <c r="L7">
-        <v>0.18016441107145345</v>
+        <v>0.20254170078674147</v>
       </c>
       <c r="M7">
-        <v>0.1619452409691271</v>
+        <v>0.1828398700353069</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -499,10 +499,10 @@
         <v>50.0</v>
       </c>
       <c r="P7">
-        <v>8.341013306196787</v>
+        <v>8.90046899886389</v>
       </c>
       <c r="Q7">
-        <v>62.52533596088071</v>
+        <v>57.54581972788225</v>
       </c>
     </row>
     <row r="8">
@@ -540,22 +540,22 @@
         </is>
       </c>
       <c r="H8">
-        <v>0.967577190262213</v>
+        <v>0.8686669773038992</v>
       </c>
       <c r="I8">
         <v>56.0</v>
       </c>
       <c r="J8">
-        <v>54.184322654683925</v>
+        <v>48.645350729018354</v>
       </c>
       <c r="K8">
-        <v>0.129443404039074</v>
+        <v>0.12002009852278538</v>
       </c>
       <c r="L8">
-        <v>0.1397977308012327</v>
+        <v>0.13656064015559286</v>
       </c>
       <c r="M8">
-        <v>0.15358524024185327</v>
+        <v>0.15067186746729072</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -566,10 +566,10 @@
         <v>50.0</v>
       </c>
       <c r="P8">
-        <v>6.4721702019537</v>
+        <v>6.001004926139268</v>
       </c>
       <c r="Q8">
-        <v>60.65649285663763</v>
+        <v>54.64635565515762</v>
       </c>
     </row>
     <row r="9">
@@ -603,26 +603,26 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0-4</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H9">
-        <v>0.967577190262213</v>
+        <v>0.8686669773038992</v>
       </c>
       <c r="I9">
         <v>56.0</v>
       </c>
       <c r="J9">
-        <v>54.184322654683925</v>
+        <v>48.645350729018354</v>
       </c>
       <c r="K9">
-        <v>0.09002251880787042</v>
+        <v>0.0864245050353621</v>
       </c>
       <c r="L9">
-        <v>0.0972235236223598</v>
+        <v>0.0983350778579698</v>
       </c>
       <c r="M9">
-        <v>0.11652236137910156</v>
+        <v>0.147949556277581</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -633,10 +633,10 @@
         <v>50.0</v>
       </c>
       <c r="P9">
-        <v>4.501125940393521</v>
+        <v>4.321225251768105</v>
       </c>
       <c r="Q9">
-        <v>58.685448595077446</v>
+        <v>52.96657598078646</v>
       </c>
     </row>
     <row r="10">
@@ -670,26 +670,26 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H10">
-        <v>0.967577190262213</v>
+        <v>0.8686669773038992</v>
       </c>
       <c r="I10">
         <v>56.0</v>
       </c>
       <c r="J10">
-        <v>54.184322654683925</v>
+        <v>48.645350729018354</v>
       </c>
       <c r="K10">
-        <v>0.0641710214370617</v>
+        <v>0.07545589839142147</v>
       </c>
       <c r="L10">
-        <v>0.0693041352450102</v>
+        <v>0.08585483527070802</v>
       </c>
       <c r="M10">
-        <v>0.10382622938369798</v>
+        <v>0.06889198339271474</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -700,10 +700,10 @@
         <v>50.0</v>
       </c>
       <c r="P10">
-        <v>3.208551071853085</v>
+        <v>3.7727949195710737</v>
       </c>
       <c r="Q10">
-        <v>57.39287372653701</v>
+        <v>52.41814564858943</v>
       </c>
     </row>
     <row r="11">
@@ -737,26 +737,26 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-4</t>
         </is>
       </c>
       <c r="H11">
-        <v>0.967577190262213</v>
+        <v>0.8686669773038992</v>
       </c>
       <c r="I11">
         <v>56.0</v>
       </c>
       <c r="J11">
-        <v>54.184322654683925</v>
+        <v>48.645350729018354</v>
       </c>
       <c r="K11">
-        <v>0.06144394507410913</v>
+        <v>0.07252791449382026</v>
       </c>
       <c r="L11">
-        <v>0.06635891690737</v>
+        <v>0.08252333196132039</v>
       </c>
       <c r="M11">
-        <v>0.053020760192704644</v>
+        <v>0.09932805759392878</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -767,10 +767,10 @@
         <v>50.0</v>
       </c>
       <c r="P11">
-        <v>3.0721972537054563</v>
+        <v>3.626395724691013</v>
       </c>
       <c r="Q11">
-        <v>57.25651990838938</v>
+        <v>52.27174645370937</v>
       </c>
     </row>
     <row r="12">
